--- a/پکیج_ارائه_کلیم_خط۱۰/فایل_اکسل_مرجع/claim metro L100.xlsx
+++ b/پکیج_ارائه_کلیم_خط۱۰/فایل_اکسل_مرجع/claim metro L100.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE28CE33-B13C-4C85-AC43-37759786483B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C0D490-73D4-4085-9293-932C719FE0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2472,7 +2472,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2481,7 +2481,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2533,7 +2533,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="7" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2559,7 +2559,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2622,7 +2622,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2634,7 +2634,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2646,7 +2646,7 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2760,15 +2760,6 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2805,22 +2796,22 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2841,7 +2832,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3237,6 +3228,21 @@
     <xf numFmtId="3" fontId="30" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3267,26 +3273,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3295,45 +3286,6 @@
     <cellStyle name="Normal 3 24 100 37 63 2 2" xfId="2" xr:uid="{6EE33E25-5F1F-43AB-81F4-E764BEA0081A}"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="B Nazanin"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="hair">
-          <color auto="1"/>
-        </left>
-        <right style="hair">
-          <color auto="1"/>
-        </right>
-        <top style="hair">
-          <color auto="1"/>
-        </top>
-        <bottom style="hair">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3470,6 +3422,45 @@
         <name val="Webdings"/>
         <family val="1"/>
         <charset val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="hair">
+          <color auto="1"/>
+        </left>
+        <right style="hair">
+          <color auto="1"/>
+        </right>
+        <top style="hair">
+          <color auto="1"/>
+        </top>
+        <bottom style="hair">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="B Nazanin"/>
+        <charset val="178"/>
         <scheme val="none"/>
       </font>
       <fill>
@@ -3736,11 +3727,11 @@
     <tableColumn id="2" xr3:uid="{50FF5458-2CB3-4748-B97D-D7B76F0F2ECA}" name="کلیم های پروژه های خط" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{CAC1899C-EE6D-4C4F-A2F1-1F2551DB825D}" name="بخشنامه، ضوابط و بندهای قراردادی" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{CD743CEF-D8CF-49D6-9710-A09518CFA394}" name="شرح اقدامات" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{5E22D058-18B9-4194-8B60-088C80904A48}" name="روش اخذ" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{2958C704-3432-4CC2-8855-311200630F9B}" name="در دست اقدام" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{97CE93F5-A0E2-4253-AADC-2F880C6E8645}" name="بار مالی اولیه(ریال)_x000a_(میزان ادعای پیمانکار)" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{2B947553-81CD-40A7-8D88-9C2F181D54D9}" name="اخذ شده(ریال)_x000a_(میزان سود حاصل از بررسی ادعا)" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{9130D879-A851-42B7-9B94-A8BFCDB01C33}" name="بار مالی نهایی(ریال)_x000a_(درصورت اخذ)" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{5E22D058-18B9-4194-8B60-088C80904A48}" name="روش اخذ" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{2958C704-3432-4CC2-8855-311200630F9B}" name="در دست اقدام" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{97CE93F5-A0E2-4253-AADC-2F880C6E8645}" name="بار مالی اولیه(ریال)_x000a_(میزان ادعای پیمانکار)" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{2B947553-81CD-40A7-8D88-9C2F181D54D9}" name="اخذ شده(ریال)_x000a_(میزان سود حاصل از بررسی ادعا)" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{9130D879-A851-42B7-9B94-A8BFCDB01C33}" name="بار مالی نهایی(ریال)_x000a_(درصورت اخذ)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4015,1492 +4006,1492 @@
   <dimension ref="A1:K97"/>
   <sheetFormatPr defaultRowHeight="22.5" outlineLevelRow="2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="134" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="137" customWidth="1"/>
-    <col min="3" max="3" width="50.28515625" style="136" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37" style="170" customWidth="1"/>
-    <col min="5" max="5" width="99.42578125" style="132" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" style="133" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" style="132" customWidth="1"/>
-    <col min="8" max="10" width="31.28515625" style="133" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" style="131" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="134" customWidth="1"/>
+    <col min="3" max="3" width="50.28515625" style="133" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37" style="167" customWidth="1"/>
+    <col min="5" max="5" width="99.42578125" style="129" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" style="130" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="129" customWidth="1"/>
+    <col min="8" max="10" width="31.28515625" style="130" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="37.7109375" style="117" customWidth="1"/>
-    <col min="13" max="13" width="20.5703125" style="117" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" style="117" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="117"/>
+    <col min="12" max="12" width="37.7109375" style="114" customWidth="1"/>
+    <col min="13" max="13" width="20.5703125" style="114" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="114"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="260"/>
-      <c r="B1" s="247" t="s">
+      <c r="A1" s="262"/>
+      <c r="B1" s="244" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="248" t="s">
+      <c r="C1" s="245" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="249" t="s">
+      <c r="D1" s="246" t="s">
         <v>284</v>
       </c>
-      <c r="E1" s="247" t="s">
+      <c r="E1" s="244" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="247" t="s">
+      <c r="F1" s="244" t="s">
         <v>331</v>
       </c>
-      <c r="G1" s="248" t="s">
+      <c r="G1" s="245" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="242" t="s">
+      <c r="H1" s="239" t="s">
         <v>214</v>
       </c>
-      <c r="I1" s="242" t="s">
+      <c r="I1" s="239" t="s">
         <v>281</v>
       </c>
-      <c r="J1" s="242" t="s">
+      <c r="J1" s="239" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24.75" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="261"/>
-      <c r="B2" s="243"/>
-      <c r="C2" s="242"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="245"/>
-      <c r="F2" s="245"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="246">
+      <c r="A2" s="263"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="243">
         <f>SUBTOTAL(9,H3:H95)-H75-H76-H77-H78-H79-H80</f>
-        <v>6348195829936.1563</v>
-      </c>
-      <c r="I2" s="246">
+        <v>6115419109936.1563</v>
+      </c>
+      <c r="I2" s="243">
         <f>SUBTOTAL(9,I3:I95)</f>
         <v>2302814643019.0303</v>
       </c>
-      <c r="J2" s="246">
+      <c r="J2" s="243">
         <f>SUBTOTAL(9,J3:J95)</f>
-        <v>22519330925880.02</v>
+        <v>22286554205880.02</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="250" t="s">
+      <c r="B3" s="247" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="171" t="s">
+      <c r="C3" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="172"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="272"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="174"/>
-      <c r="J3" s="174"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="257"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
     </row>
     <row r="4" spans="1:10" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="248" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="175" t="s">
+      <c r="C4" s="172" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="176"/>
-      <c r="E4" s="177" t="s">
+      <c r="D4" s="173"/>
+      <c r="E4" s="174" t="s">
         <v>212</v>
       </c>
-      <c r="F4" s="273"/>
-      <c r="G4" s="178"/>
-      <c r="H4" s="179">
-        <f>(374+402)*300000000</f>
-        <v>232800000000</v>
-      </c>
-      <c r="I4" s="179"/>
-      <c r="J4" s="179">
+      <c r="F4" s="258"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="176">
+        <f>(374+402)*30000</f>
+        <v>23280000</v>
+      </c>
+      <c r="I4" s="176"/>
+      <c r="J4" s="176">
         <f>Table1[[#This Row],[بار مالی اولیه(ریال)
 (میزان ادعای پیمانکار)]]</f>
-        <v>232800000000</v>
+        <v>23280000</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="240"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="181"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="274"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="184"/>
+      <c r="B5" s="237"/>
+      <c r="C5" s="177"/>
+      <c r="D5" s="178"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="259"/>
+      <c r="G5" s="180"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="181"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="250" t="s">
+      <c r="B6" s="247" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="185" t="s">
+      <c r="C6" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="186"/>
-      <c r="E6" s="187"/>
-      <c r="F6" s="275"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="189"/>
-      <c r="I6" s="189"/>
-      <c r="J6" s="189"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="260"/>
+      <c r="G6" s="185"/>
+      <c r="H6" s="186"/>
+      <c r="I6" s="186"/>
+      <c r="J6" s="186"/>
     </row>
     <row r="7" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B7" s="251" t="s">
+      <c r="B7" s="248" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="190" t="s">
+      <c r="C7" s="187" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="191"/>
-      <c r="E7" s="177" t="s">
+      <c r="D7" s="188"/>
+      <c r="E7" s="174" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="273"/>
-      <c r="G7" s="178"/>
-      <c r="H7" s="179"/>
-      <c r="I7" s="179"/>
-      <c r="J7" s="179"/>
+      <c r="F7" s="258"/>
+      <c r="G7" s="175"/>
+      <c r="H7" s="176"/>
+      <c r="I7" s="176"/>
+      <c r="J7" s="176"/>
     </row>
     <row r="8" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B8" s="252" t="s">
+      <c r="B8" s="249" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="192" t="s">
+      <c r="C8" s="189" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="193"/>
-      <c r="E8" s="194" t="s">
+      <c r="D8" s="190"/>
+      <c r="E8" s="191" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="211"/>
-      <c r="G8" s="195"/>
-      <c r="H8" s="196"/>
-      <c r="I8" s="196"/>
-      <c r="J8" s="196"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="192"/>
+      <c r="H8" s="193"/>
+      <c r="I8" s="193"/>
+      <c r="J8" s="193"/>
     </row>
     <row r="9" spans="1:10" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="240"/>
-      <c r="C9" s="180"/>
-      <c r="D9" s="181"/>
-      <c r="E9" s="197"/>
-      <c r="F9" s="180"/>
-      <c r="G9" s="198"/>
-      <c r="H9" s="184"/>
-      <c r="I9" s="184"/>
-      <c r="J9" s="184"/>
+      <c r="B9" s="237"/>
+      <c r="C9" s="177"/>
+      <c r="D9" s="178"/>
+      <c r="E9" s="194"/>
+      <c r="F9" s="177"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="181"/>
+      <c r="I9" s="181"/>
+      <c r="J9" s="181"/>
     </row>
     <row r="10" spans="1:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="250" t="s">
+      <c r="B10" s="247" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="185" t="s">
+      <c r="C10" s="182" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="186"/>
-      <c r="E10" s="199"/>
-      <c r="F10" s="220"/>
-      <c r="G10" s="200"/>
-      <c r="H10" s="189"/>
-      <c r="I10" s="189"/>
-      <c r="J10" s="189"/>
+      <c r="D10" s="183"/>
+      <c r="E10" s="196"/>
+      <c r="F10" s="217"/>
+      <c r="G10" s="197"/>
+      <c r="H10" s="186"/>
+      <c r="I10" s="186"/>
+      <c r="J10" s="186"/>
     </row>
     <row r="11" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B11" s="251" t="s">
+      <c r="B11" s="248" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="175" t="s">
+      <c r="C11" s="172" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="176"/>
-      <c r="E11" s="177" t="s">
+      <c r="D11" s="173"/>
+      <c r="E11" s="174" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="273"/>
-      <c r="G11" s="178"/>
-      <c r="H11" s="179"/>
-      <c r="I11" s="179"/>
-      <c r="J11" s="179"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
     </row>
     <row r="12" spans="1:10" ht="63" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B12" s="252" t="s">
+      <c r="B12" s="249" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="201" t="s">
+      <c r="C12" s="198" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="202" t="s">
+      <c r="D12" s="199" t="s">
         <v>286</v>
       </c>
-      <c r="E12" s="203" t="s">
+      <c r="E12" s="200" t="s">
         <v>274</v>
       </c>
-      <c r="F12" s="201" t="s">
+      <c r="F12" s="198" t="s">
         <v>333</v>
       </c>
-      <c r="G12" s="195" t="s">
+      <c r="G12" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H12" s="196">
+      <c r="H12" s="193">
         <v>134402080225</v>
       </c>
-      <c r="I12" s="196">
+      <c r="I12" s="193">
         <f>Table1[[#This Row],[بار مالی اولیه(ریال)
 (میزان ادعای پیمانکار)]]*0.7</f>
         <v>94081456157.5</v>
       </c>
-      <c r="J12" s="196">
+      <c r="J12" s="193">
         <f>Table1[[#This Row],[بار مالی اولیه(ریال)
 (میزان ادعای پیمانکار)]]</f>
         <v>134402080225</v>
       </c>
     </row>
     <row r="13" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B13" s="252" t="s">
+      <c r="B13" s="249" t="s">
         <v>227</v>
       </c>
-      <c r="C13" s="192" t="s">
+      <c r="C13" s="189" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="193"/>
-      <c r="E13" s="194" t="s">
+      <c r="D13" s="190"/>
+      <c r="E13" s="191" t="s">
         <v>105</v>
       </c>
-      <c r="F13" s="211"/>
-      <c r="G13" s="195"/>
-      <c r="H13" s="196"/>
-      <c r="I13" s="196"/>
-      <c r="J13" s="196"/>
+      <c r="F13" s="208"/>
+      <c r="G13" s="192"/>
+      <c r="H13" s="193"/>
+      <c r="I13" s="193"/>
+      <c r="J13" s="193"/>
     </row>
     <row r="14" spans="1:10" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="240"/>
-      <c r="C14" s="180"/>
-      <c r="D14" s="181"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="216"/>
-      <c r="G14" s="205"/>
-      <c r="H14" s="184"/>
-      <c r="I14" s="184"/>
-      <c r="J14" s="184"/>
+      <c r="B14" s="237"/>
+      <c r="C14" s="177"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="201"/>
+      <c r="F14" s="213"/>
+      <c r="G14" s="202"/>
+      <c r="H14" s="181"/>
+      <c r="I14" s="181"/>
+      <c r="J14" s="181"/>
     </row>
     <row r="15" spans="1:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="250" t="s">
+      <c r="B15" s="247" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="185" t="s">
+      <c r="C15" s="182" t="s">
         <v>193</v>
       </c>
-      <c r="D15" s="186"/>
-      <c r="E15" s="199"/>
-      <c r="F15" s="220"/>
-      <c r="G15" s="200"/>
-      <c r="H15" s="189"/>
-      <c r="I15" s="189"/>
-      <c r="J15" s="189"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="196"/>
+      <c r="F15" s="217"/>
+      <c r="G15" s="197"/>
+      <c r="H15" s="186"/>
+      <c r="I15" s="186"/>
+      <c r="J15" s="186"/>
     </row>
     <row r="16" spans="1:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B16" s="251" t="s">
+      <c r="B16" s="248" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="175" t="s">
+      <c r="C16" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="176"/>
-      <c r="E16" s="177" t="s">
+      <c r="D16" s="173"/>
+      <c r="E16" s="174" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="273"/>
-      <c r="G16" s="178"/>
-      <c r="H16" s="179"/>
-      <c r="I16" s="179"/>
-      <c r="J16" s="179"/>
+      <c r="F16" s="258"/>
+      <c r="G16" s="175"/>
+      <c r="H16" s="176"/>
+      <c r="I16" s="176"/>
+      <c r="J16" s="176"/>
     </row>
     <row r="17" spans="2:11" ht="45" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B17" s="252" t="s">
+      <c r="B17" s="249" t="s">
         <v>150</v>
       </c>
-      <c r="C17" s="201" t="s">
+      <c r="C17" s="198" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="202" t="s">
+      <c r="D17" s="199" t="s">
         <v>286</v>
       </c>
-      <c r="E17" s="203" t="s">
+      <c r="E17" s="200" t="s">
         <v>234</v>
       </c>
-      <c r="F17" s="201" t="s">
+      <c r="F17" s="198" t="s">
         <v>333</v>
       </c>
-      <c r="G17" s="195" t="s">
+      <c r="G17" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H17" s="196">
+      <c r="H17" s="193">
         <f>35779531251*1.3</f>
         <v>46513390626.300003</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="193">
         <f>Table1[[#This Row],[بار مالی اولیه(ریال)
 (میزان ادعای پیمانکار)]]*0.7</f>
         <v>32559373438.41</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="193">
         <f>Table1[[#This Row],[بار مالی اولیه(ریال)
 (میزان ادعای پیمانکار)]]</f>
         <v>46513390626.300003</v>
       </c>
     </row>
     <row r="18" spans="2:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B18" s="252" t="s">
+      <c r="B18" s="249" t="s">
         <v>151</v>
       </c>
-      <c r="C18" s="201" t="s">
+      <c r="C18" s="198" t="s">
         <v>239</v>
       </c>
-      <c r="D18" s="202"/>
-      <c r="E18" s="203" t="s">
+      <c r="D18" s="199"/>
+      <c r="E18" s="200" t="s">
         <v>240</v>
       </c>
-      <c r="F18" s="201"/>
-      <c r="G18" s="206" t="s">
+      <c r="F18" s="198"/>
+      <c r="G18" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H18" s="207">
+      <c r="H18" s="204">
         <v>107200000000</v>
       </c>
-      <c r="I18" s="207">
+      <c r="I18" s="204">
         <v>107200000000</v>
       </c>
-      <c r="J18" s="207">
+      <c r="J18" s="204">
         <f>Table1[[#This Row],[بار مالی اولیه(ریال)
 (میزان ادعای پیمانکار)]]</f>
         <v>107200000000</v>
       </c>
     </row>
     <row r="19" spans="2:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B19" s="252"/>
-      <c r="C19" s="192"/>
-      <c r="D19" s="193"/>
-      <c r="E19" s="194"/>
-      <c r="F19" s="211"/>
-      <c r="G19" s="195"/>
-      <c r="H19" s="196"/>
-      <c r="I19" s="196"/>
-      <c r="J19" s="196"/>
+      <c r="B19" s="249"/>
+      <c r="C19" s="189"/>
+      <c r="D19" s="190"/>
+      <c r="E19" s="191"/>
+      <c r="F19" s="208"/>
+      <c r="G19" s="192"/>
+      <c r="H19" s="193"/>
+      <c r="I19" s="193"/>
+      <c r="J19" s="193"/>
     </row>
     <row r="20" spans="2:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B20" s="252"/>
-      <c r="C20" s="192" t="s">
+      <c r="B20" s="249"/>
+      <c r="C20" s="189" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="193"/>
-      <c r="E20" s="194" t="s">
+      <c r="D20" s="190"/>
+      <c r="E20" s="191" t="s">
         <v>110</v>
       </c>
-      <c r="F20" s="211"/>
-      <c r="G20" s="195"/>
-      <c r="H20" s="196"/>
-      <c r="I20" s="196"/>
-      <c r="J20" s="196"/>
+      <c r="F20" s="208"/>
+      <c r="G20" s="192"/>
+      <c r="H20" s="193"/>
+      <c r="I20" s="193"/>
+      <c r="J20" s="193"/>
     </row>
     <row r="21" spans="2:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B21" s="252"/>
-      <c r="C21" s="192" t="s">
+      <c r="B21" s="249"/>
+      <c r="C21" s="189" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="193"/>
-      <c r="E21" s="194" t="s">
+      <c r="D21" s="190"/>
+      <c r="E21" s="191" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="211"/>
-      <c r="G21" s="195"/>
-      <c r="H21" s="196"/>
-      <c r="I21" s="196"/>
-      <c r="J21" s="196"/>
+      <c r="F21" s="208"/>
+      <c r="G21" s="192"/>
+      <c r="H21" s="193"/>
+      <c r="I21" s="193"/>
+      <c r="J21" s="193"/>
     </row>
     <row r="22" spans="2:11" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="240"/>
-      <c r="C22" s="180"/>
-      <c r="D22" s="181"/>
-      <c r="E22" s="197"/>
-      <c r="F22" s="180"/>
-      <c r="G22" s="198"/>
-      <c r="H22" s="184"/>
-      <c r="I22" s="184"/>
-      <c r="J22" s="184"/>
+      <c r="B22" s="237"/>
+      <c r="C22" s="177"/>
+      <c r="D22" s="178"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="195"/>
+      <c r="H22" s="181"/>
+      <c r="I22" s="181"/>
+      <c r="J22" s="181"/>
     </row>
     <row r="23" spans="2:11" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="250" t="s">
+      <c r="B23" s="247" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="185" t="s">
+      <c r="C23" s="182" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="186"/>
-      <c r="E23" s="199"/>
-      <c r="F23" s="220"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="189"/>
-      <c r="I23" s="189"/>
-      <c r="J23" s="189"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="196"/>
+      <c r="F23" s="217"/>
+      <c r="G23" s="197"/>
+      <c r="H23" s="186"/>
+      <c r="I23" s="186"/>
+      <c r="J23" s="186"/>
     </row>
     <row r="24" spans="2:11" ht="105" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B24" s="251" t="s">
+      <c r="B24" s="248" t="s">
         <v>146</v>
       </c>
-      <c r="C24" s="190" t="s">
+      <c r="C24" s="187" t="s">
         <v>129</v>
       </c>
-      <c r="D24" s="191"/>
-      <c r="E24" s="208" t="s">
+      <c r="D24" s="188"/>
+      <c r="E24" s="205" t="s">
         <v>127</v>
       </c>
-      <c r="F24" s="190"/>
-      <c r="G24" s="209" t="s">
+      <c r="F24" s="187"/>
+      <c r="G24" s="206" t="s">
         <v>176</v>
       </c>
-      <c r="H24" s="210"/>
-      <c r="I24" s="210"/>
-      <c r="J24" s="210"/>
+      <c r="H24" s="207"/>
+      <c r="I24" s="207"/>
+      <c r="J24" s="207"/>
     </row>
     <row r="25" spans="2:11" ht="147" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B25" s="252" t="s">
+      <c r="B25" s="249" t="s">
         <v>147</v>
       </c>
-      <c r="C25" s="201" t="s">
+      <c r="C25" s="198" t="s">
         <v>140</v>
       </c>
-      <c r="D25" s="202" t="s">
+      <c r="D25" s="199" t="s">
         <v>285</v>
       </c>
-      <c r="E25" s="194" t="s">
+      <c r="E25" s="191" t="s">
         <v>245</v>
       </c>
-      <c r="F25" s="211" t="s">
+      <c r="F25" s="208" t="s">
         <v>334</v>
       </c>
-      <c r="G25" s="195" t="s">
+      <c r="G25" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H25" s="196"/>
-      <c r="I25" s="196"/>
-      <c r="J25" s="196"/>
+      <c r="H25" s="193"/>
+      <c r="I25" s="193"/>
+      <c r="J25" s="193"/>
       <c r="K25" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="147" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B26" s="252" t="s">
+      <c r="B26" s="249" t="s">
         <v>148</v>
       </c>
-      <c r="C26" s="201" t="s">
+      <c r="C26" s="198" t="s">
         <v>141</v>
       </c>
-      <c r="D26" s="202" t="s">
+      <c r="D26" s="199" t="s">
         <v>285</v>
       </c>
-      <c r="E26" s="194" t="s">
+      <c r="E26" s="191" t="s">
         <v>245</v>
       </c>
-      <c r="F26" s="211" t="s">
+      <c r="F26" s="208" t="s">
         <v>334</v>
       </c>
-      <c r="G26" s="195" t="s">
+      <c r="G26" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H26" s="196"/>
-      <c r="I26" s="196"/>
-      <c r="J26" s="196"/>
+      <c r="H26" s="193"/>
+      <c r="I26" s="193"/>
+      <c r="J26" s="193"/>
     </row>
     <row r="27" spans="2:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B27" s="252" t="s">
+      <c r="B27" s="249" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="201" t="s">
+      <c r="C27" s="198" t="s">
         <v>179</v>
       </c>
-      <c r="D27" s="202" t="s">
+      <c r="D27" s="199" t="s">
         <v>287</v>
       </c>
-      <c r="E27" s="194" t="s">
+      <c r="E27" s="191" t="s">
         <v>181</v>
       </c>
-      <c r="F27" s="211"/>
-      <c r="G27" s="195"/>
-      <c r="H27" s="196"/>
-      <c r="I27" s="196"/>
-      <c r="J27" s="196"/>
+      <c r="F27" s="208"/>
+      <c r="G27" s="192"/>
+      <c r="H27" s="193"/>
+      <c r="I27" s="193"/>
+      <c r="J27" s="193"/>
     </row>
     <row r="28" spans="2:11" ht="63" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B28" s="252" t="s">
+      <c r="B28" s="249" t="s">
         <v>184</v>
       </c>
-      <c r="C28" s="201" t="s">
+      <c r="C28" s="198" t="s">
         <v>180</v>
       </c>
-      <c r="D28" s="202" t="s">
+      <c r="D28" s="199" t="s">
         <v>291</v>
       </c>
-      <c r="E28" s="194" t="s">
+      <c r="E28" s="191" t="s">
         <v>275</v>
       </c>
-      <c r="F28" s="211" t="s">
+      <c r="F28" s="208" t="s">
         <v>334</v>
       </c>
-      <c r="G28" s="195" t="s">
+      <c r="G28" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H28" s="196"/>
-      <c r="I28" s="196"/>
-      <c r="J28" s="196"/>
+      <c r="H28" s="193"/>
+      <c r="I28" s="193"/>
+      <c r="J28" s="193"/>
     </row>
     <row r="29" spans="2:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B29" s="252" t="s">
+      <c r="B29" s="249" t="s">
         <v>185</v>
       </c>
-      <c r="C29" s="201" t="s">
+      <c r="C29" s="198" t="s">
         <v>186</v>
       </c>
-      <c r="D29" s="202"/>
-      <c r="E29" s="194" t="s">
+      <c r="D29" s="199"/>
+      <c r="E29" s="191" t="s">
         <v>182</v>
       </c>
-      <c r="F29" s="211"/>
-      <c r="G29" s="195"/>
-      <c r="H29" s="196"/>
-      <c r="I29" s="196"/>
-      <c r="J29" s="196"/>
+      <c r="F29" s="208"/>
+      <c r="G29" s="192"/>
+      <c r="H29" s="193"/>
+      <c r="I29" s="193"/>
+      <c r="J29" s="193"/>
     </row>
     <row r="30" spans="2:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B30" s="252" t="s">
+      <c r="B30" s="249" t="s">
         <v>236</v>
       </c>
-      <c r="C30" s="201" t="s">
+      <c r="C30" s="198" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="202"/>
-      <c r="E30" s="203" t="s">
+      <c r="D30" s="199"/>
+      <c r="E30" s="200" t="s">
         <v>238</v>
       </c>
-      <c r="F30" s="201" t="s">
+      <c r="F30" s="198" t="s">
         <v>332</v>
       </c>
-      <c r="G30" s="206" t="s">
+      <c r="G30" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H30" s="207">
+      <c r="H30" s="204">
         <v>35000000000</v>
       </c>
-      <c r="I30" s="207">
+      <c r="I30" s="204">
         <v>35000000000</v>
       </c>
-      <c r="J30" s="207">
+      <c r="J30" s="204">
         <f>Table1[[#This Row],[بار مالی اولیه(ریال)
 (میزان ادعای پیمانکار)]]</f>
         <v>35000000000</v>
       </c>
     </row>
     <row r="31" spans="2:11" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B31" s="241"/>
-      <c r="C31" s="211" t="s">
+      <c r="B31" s="238"/>
+      <c r="C31" s="208" t="s">
         <v>277</v>
       </c>
-      <c r="D31" s="212"/>
-      <c r="E31" s="203" t="s">
+      <c r="D31" s="209"/>
+      <c r="E31" s="200" t="s">
         <v>278</v>
       </c>
-      <c r="F31" s="201"/>
-      <c r="G31" s="195"/>
-      <c r="H31" s="196"/>
-      <c r="I31" s="196"/>
-      <c r="J31" s="196"/>
+      <c r="F31" s="198"/>
+      <c r="G31" s="192"/>
+      <c r="H31" s="193"/>
+      <c r="I31" s="193"/>
+      <c r="J31" s="193"/>
     </row>
     <row r="32" spans="2:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B32" s="241"/>
-      <c r="C32" s="211"/>
-      <c r="D32" s="212"/>
-      <c r="E32" s="194"/>
-      <c r="F32" s="211"/>
-      <c r="G32" s="195"/>
-      <c r="H32" s="196"/>
-      <c r="I32" s="196"/>
-      <c r="J32" s="196"/>
+      <c r="B32" s="238"/>
+      <c r="C32" s="208"/>
+      <c r="D32" s="209"/>
+      <c r="E32" s="191"/>
+      <c r="F32" s="208"/>
+      <c r="G32" s="192"/>
+      <c r="H32" s="193"/>
+      <c r="I32" s="193"/>
+      <c r="J32" s="193"/>
     </row>
     <row r="33" spans="2:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B33" s="241"/>
-      <c r="C33" s="211"/>
-      <c r="D33" s="212"/>
-      <c r="E33" s="194"/>
-      <c r="F33" s="211"/>
-      <c r="G33" s="195"/>
-      <c r="H33" s="196"/>
-      <c r="I33" s="196"/>
-      <c r="J33" s="196"/>
+      <c r="B33" s="238"/>
+      <c r="C33" s="208"/>
+      <c r="D33" s="209"/>
+      <c r="E33" s="191"/>
+      <c r="F33" s="208"/>
+      <c r="G33" s="192"/>
+      <c r="H33" s="193"/>
+      <c r="I33" s="193"/>
+      <c r="J33" s="193"/>
     </row>
     <row r="34" spans="2:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B34" s="241"/>
-      <c r="C34" s="211"/>
-      <c r="D34" s="212"/>
-      <c r="E34" s="194"/>
-      <c r="F34" s="211"/>
-      <c r="G34" s="195"/>
-      <c r="H34" s="196"/>
-      <c r="I34" s="196"/>
-      <c r="J34" s="196"/>
+      <c r="B34" s="238"/>
+      <c r="C34" s="208"/>
+      <c r="D34" s="209"/>
+      <c r="E34" s="191"/>
+      <c r="F34" s="208"/>
+      <c r="G34" s="192"/>
+      <c r="H34" s="193"/>
+      <c r="I34" s="193"/>
+      <c r="J34" s="193"/>
     </row>
     <row r="35" spans="2:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B35" s="241"/>
-      <c r="C35" s="211"/>
-      <c r="D35" s="212"/>
-      <c r="E35" s="194"/>
-      <c r="F35" s="211"/>
-      <c r="G35" s="195"/>
-      <c r="H35" s="196"/>
-      <c r="I35" s="196"/>
-      <c r="J35" s="196"/>
+      <c r="B35" s="238"/>
+      <c r="C35" s="208"/>
+      <c r="D35" s="209"/>
+      <c r="E35" s="191"/>
+      <c r="F35" s="208"/>
+      <c r="G35" s="192"/>
+      <c r="H35" s="193"/>
+      <c r="I35" s="193"/>
+      <c r="J35" s="193"/>
     </row>
     <row r="36" spans="2:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B36" s="241"/>
-      <c r="C36" s="211"/>
-      <c r="D36" s="212"/>
-      <c r="E36" s="194"/>
-      <c r="F36" s="211"/>
-      <c r="G36" s="195"/>
-      <c r="H36" s="196"/>
-      <c r="I36" s="196"/>
-      <c r="J36" s="196"/>
+      <c r="B36" s="238"/>
+      <c r="C36" s="208"/>
+      <c r="D36" s="209"/>
+      <c r="E36" s="191"/>
+      <c r="F36" s="208"/>
+      <c r="G36" s="192"/>
+      <c r="H36" s="193"/>
+      <c r="I36" s="193"/>
+      <c r="J36" s="193"/>
     </row>
     <row r="37" spans="2:10" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="241"/>
-      <c r="C37" s="211"/>
-      <c r="D37" s="212"/>
-      <c r="E37" s="194"/>
-      <c r="F37" s="211"/>
-      <c r="G37" s="195"/>
-      <c r="H37" s="196"/>
-      <c r="I37" s="196"/>
-      <c r="J37" s="196"/>
+      <c r="B37" s="238"/>
+      <c r="C37" s="208"/>
+      <c r="D37" s="209"/>
+      <c r="E37" s="191"/>
+      <c r="F37" s="208"/>
+      <c r="G37" s="192"/>
+      <c r="H37" s="193"/>
+      <c r="I37" s="193"/>
+      <c r="J37" s="193"/>
     </row>
     <row r="38" spans="2:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="250" t="s">
+      <c r="B38" s="247" t="s">
         <v>119</v>
       </c>
-      <c r="C38" s="185" t="s">
+      <c r="C38" s="182" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="186"/>
-      <c r="E38" s="199"/>
-      <c r="F38" s="220"/>
-      <c r="G38" s="200"/>
-      <c r="H38" s="189"/>
-      <c r="I38" s="189"/>
-      <c r="J38" s="189"/>
+      <c r="D38" s="183"/>
+      <c r="E38" s="196"/>
+      <c r="F38" s="217"/>
+      <c r="G38" s="197"/>
+      <c r="H38" s="186"/>
+      <c r="I38" s="186"/>
+      <c r="J38" s="186"/>
     </row>
     <row r="39" spans="2:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B39" s="241"/>
-      <c r="C39" s="211" t="s">
+      <c r="B39" s="238"/>
+      <c r="C39" s="208" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="212"/>
-      <c r="E39" s="194" t="s">
+      <c r="D39" s="209"/>
+      <c r="E39" s="191" t="s">
         <v>46</v>
       </c>
-      <c r="F39" s="211"/>
-      <c r="G39" s="195"/>
-      <c r="H39" s="196"/>
-      <c r="I39" s="196"/>
-      <c r="J39" s="196"/>
+      <c r="F39" s="208"/>
+      <c r="G39" s="192"/>
+      <c r="H39" s="193"/>
+      <c r="I39" s="193"/>
+      <c r="J39" s="193"/>
     </row>
     <row r="40" spans="2:10" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="241"/>
-      <c r="C40" s="211"/>
-      <c r="D40" s="212"/>
-      <c r="E40" s="194"/>
-      <c r="F40" s="211"/>
-      <c r="G40" s="195"/>
-      <c r="H40" s="196"/>
-      <c r="I40" s="196"/>
-      <c r="J40" s="196"/>
+      <c r="B40" s="238"/>
+      <c r="C40" s="208"/>
+      <c r="D40" s="209"/>
+      <c r="E40" s="191"/>
+      <c r="F40" s="208"/>
+      <c r="G40" s="192"/>
+      <c r="H40" s="193"/>
+      <c r="I40" s="193"/>
+      <c r="J40" s="193"/>
     </row>
     <row r="41" spans="2:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="250" t="s">
+      <c r="B41" s="247" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="185" t="s">
+      <c r="C41" s="182" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="186"/>
-      <c r="E41" s="199"/>
-      <c r="F41" s="220"/>
-      <c r="G41" s="200"/>
-      <c r="H41" s="189"/>
-      <c r="I41" s="189"/>
-      <c r="J41" s="189"/>
+      <c r="D41" s="183"/>
+      <c r="E41" s="196"/>
+      <c r="F41" s="217"/>
+      <c r="G41" s="197"/>
+      <c r="H41" s="186"/>
+      <c r="I41" s="186"/>
+      <c r="J41" s="186"/>
     </row>
     <row r="42" spans="2:10" ht="60.75" customHeight="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="252" t="s">
+      <c r="B42" s="249" t="s">
         <v>156</v>
       </c>
-      <c r="C42" s="201" t="s">
+      <c r="C42" s="198" t="s">
         <v>139</v>
       </c>
-      <c r="D42" s="202" t="s">
+      <c r="D42" s="199" t="s">
         <v>286</v>
       </c>
-      <c r="E42" s="203" t="s">
+      <c r="E42" s="200" t="s">
         <v>233</v>
       </c>
-      <c r="F42" s="201" t="s">
+      <c r="F42" s="198" t="s">
         <v>333</v>
       </c>
-      <c r="G42" s="206" t="s">
+      <c r="G42" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H42" s="207">
+      <c r="H42" s="204">
         <f>953385000*1.3</f>
         <v>1239400500</v>
       </c>
-      <c r="I42" s="207">
+      <c r="I42" s="204">
         <f>Table1[[#This Row],[بار مالی اولیه(ریال)
 (میزان ادعای پیمانکار)]]*0.7</f>
         <v>867580350</v>
       </c>
-      <c r="J42" s="207">
+      <c r="J42" s="204">
         <f>Table1[[#This Row],[بار مالی اولیه(ریال)
 (میزان ادعای پیمانکار)]]</f>
         <v>1239400500</v>
       </c>
     </row>
     <row r="43" spans="2:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="250" t="s">
+      <c r="B43" s="247" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="185" t="s">
+      <c r="C43" s="182" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="186"/>
-      <c r="E43" s="199"/>
-      <c r="F43" s="220"/>
-      <c r="G43" s="200"/>
-      <c r="H43" s="189"/>
-      <c r="I43" s="189"/>
-      <c r="J43" s="189"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="196"/>
+      <c r="F43" s="217"/>
+      <c r="G43" s="197"/>
+      <c r="H43" s="186"/>
+      <c r="I43" s="186"/>
+      <c r="J43" s="186"/>
     </row>
     <row r="44" spans="2:10" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="252"/>
-      <c r="C44" s="201" t="s">
+      <c r="B44" s="249"/>
+      <c r="C44" s="198" t="s">
         <v>143</v>
       </c>
-      <c r="D44" s="202"/>
-      <c r="E44" s="194" t="s">
+      <c r="D44" s="199"/>
+      <c r="E44" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="F44" s="211"/>
-      <c r="G44" s="195"/>
-      <c r="H44" s="196"/>
-      <c r="I44" s="196"/>
-      <c r="J44" s="196"/>
+      <c r="F44" s="208"/>
+      <c r="G44" s="192"/>
+      <c r="H44" s="193"/>
+      <c r="I44" s="193"/>
+      <c r="J44" s="193"/>
     </row>
     <row r="45" spans="2:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="250" t="s">
+      <c r="B45" s="247" t="s">
         <v>122</v>
       </c>
-      <c r="C45" s="185" t="s">
+      <c r="C45" s="182" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="186"/>
-      <c r="E45" s="199"/>
-      <c r="F45" s="220"/>
-      <c r="G45" s="200"/>
-      <c r="H45" s="189"/>
-      <c r="I45" s="189"/>
-      <c r="J45" s="189"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="196"/>
+      <c r="F45" s="217"/>
+      <c r="G45" s="197"/>
+      <c r="H45" s="186"/>
+      <c r="I45" s="186"/>
+      <c r="J45" s="186"/>
     </row>
     <row r="46" spans="2:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B46" s="241"/>
-      <c r="C46" s="253" t="s">
+      <c r="B46" s="238"/>
+      <c r="C46" s="250" t="s">
         <v>98</v>
       </c>
-      <c r="D46" s="254"/>
-      <c r="E46" s="213" t="s">
+      <c r="D46" s="251"/>
+      <c r="E46" s="210" t="s">
         <v>99</v>
       </c>
-      <c r="F46" s="253"/>
-      <c r="G46" s="214"/>
-      <c r="H46" s="215"/>
-      <c r="I46" s="215"/>
-      <c r="J46" s="215"/>
+      <c r="F46" s="250"/>
+      <c r="G46" s="211"/>
+      <c r="H46" s="212"/>
+      <c r="I46" s="212"/>
+      <c r="J46" s="212"/>
     </row>
     <row r="47" spans="2:10" ht="42.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="241"/>
-      <c r="C47" s="211" t="s">
+      <c r="B47" s="238"/>
+      <c r="C47" s="208" t="s">
         <v>64</v>
       </c>
-      <c r="D47" s="212"/>
-      <c r="E47" s="194" t="s">
+      <c r="D47" s="209"/>
+      <c r="E47" s="191" t="s">
         <v>65</v>
       </c>
-      <c r="F47" s="211"/>
-      <c r="G47" s="195"/>
-      <c r="H47" s="196"/>
-      <c r="I47" s="196"/>
-      <c r="J47" s="196"/>
+      <c r="F47" s="208"/>
+      <c r="G47" s="192"/>
+      <c r="H47" s="193"/>
+      <c r="I47" s="193"/>
+      <c r="J47" s="193"/>
     </row>
     <row r="48" spans="2:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="250" t="s">
+      <c r="B48" s="247" t="s">
         <v>123</v>
       </c>
-      <c r="C48" s="185" t="s">
+      <c r="C48" s="182" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="186"/>
-      <c r="E48" s="199"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="200"/>
-      <c r="H48" s="189"/>
-      <c r="I48" s="189"/>
-      <c r="J48" s="189"/>
+      <c r="D48" s="183"/>
+      <c r="E48" s="196"/>
+      <c r="F48" s="217"/>
+      <c r="G48" s="197"/>
+      <c r="H48" s="186"/>
+      <c r="I48" s="186"/>
+      <c r="J48" s="186"/>
     </row>
     <row r="49" spans="2:10" ht="168" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B49" s="251" t="s">
+      <c r="B49" s="248" t="s">
         <v>158</v>
       </c>
-      <c r="C49" s="190" t="s">
+      <c r="C49" s="187" t="s">
         <v>128</v>
       </c>
-      <c r="D49" s="191" t="s">
+      <c r="D49" s="188" t="s">
         <v>288</v>
       </c>
-      <c r="E49" s="208" t="s">
+      <c r="E49" s="205" t="s">
         <v>335</v>
       </c>
-      <c r="F49" s="190"/>
-      <c r="G49" s="178" t="s">
+      <c r="F49" s="187"/>
+      <c r="G49" s="175" t="s">
         <v>176</v>
       </c>
-      <c r="H49" s="179"/>
-      <c r="I49" s="179"/>
-      <c r="J49" s="179"/>
+      <c r="H49" s="176"/>
+      <c r="I49" s="176"/>
+      <c r="J49" s="176"/>
     </row>
     <row r="50" spans="2:10" ht="189" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B50" s="252" t="s">
+      <c r="B50" s="249" t="s">
         <v>159</v>
       </c>
-      <c r="C50" s="201" t="s">
+      <c r="C50" s="198" t="s">
         <v>269</v>
       </c>
-      <c r="D50" s="202" t="s">
+      <c r="D50" s="199" t="s">
         <v>289</v>
       </c>
-      <c r="E50" s="203" t="s">
+      <c r="E50" s="200" t="s">
         <v>325</v>
       </c>
-      <c r="F50" s="201" t="s">
+      <c r="F50" s="198" t="s">
         <v>332</v>
       </c>
-      <c r="G50" s="195" t="s">
+      <c r="G50" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H50" s="196">
+      <c r="H50" s="193">
         <v>735415334655.45605</v>
       </c>
-      <c r="I50" s="196">
+      <c r="I50" s="193">
         <v>177653825323</v>
       </c>
-      <c r="J50" s="196">
+      <c r="J50" s="193">
         <v>4464347424892</v>
       </c>
     </row>
     <row r="51" spans="2:10" ht="231" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B51" s="252" t="s">
+      <c r="B51" s="249" t="s">
         <v>160</v>
       </c>
-      <c r="C51" s="201" t="s">
+      <c r="C51" s="198" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="202" t="s">
+      <c r="D51" s="199" t="s">
         <v>290</v>
       </c>
-      <c r="E51" s="203" t="s">
+      <c r="E51" s="200" t="s">
         <v>327</v>
       </c>
-      <c r="F51" s="201" t="s">
+      <c r="F51" s="198" t="s">
         <v>336</v>
       </c>
-      <c r="G51" s="195" t="s">
+      <c r="G51" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H51" s="196"/>
-      <c r="I51" s="196"/>
-      <c r="J51" s="196"/>
+      <c r="H51" s="193"/>
+      <c r="I51" s="193"/>
+      <c r="J51" s="193"/>
     </row>
     <row r="52" spans="2:10" ht="84" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B52" s="252" t="s">
+      <c r="B52" s="249" t="s">
         <v>161</v>
       </c>
-      <c r="C52" s="201" t="s">
+      <c r="C52" s="198" t="s">
         <v>142</v>
       </c>
-      <c r="D52" s="202"/>
-      <c r="E52" s="203" t="s">
+      <c r="D52" s="199"/>
+      <c r="E52" s="200" t="s">
         <v>226</v>
       </c>
-      <c r="F52" s="201"/>
-      <c r="G52" s="206" t="s">
+      <c r="F52" s="198"/>
+      <c r="G52" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H52" s="207"/>
-      <c r="I52" s="207"/>
-      <c r="J52" s="207"/>
+      <c r="H52" s="204"/>
+      <c r="I52" s="204"/>
+      <c r="J52" s="204"/>
     </row>
     <row r="53" spans="2:10" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B53" s="252" t="s">
+      <c r="B53" s="249" t="s">
         <v>169</v>
       </c>
-      <c r="C53" s="201" t="s">
+      <c r="C53" s="198" t="s">
         <v>270</v>
       </c>
-      <c r="D53" s="202"/>
-      <c r="E53" s="203" t="s">
+      <c r="D53" s="199"/>
+      <c r="E53" s="200" t="s">
         <v>171</v>
       </c>
-      <c r="F53" s="201" t="s">
+      <c r="F53" s="198" t="s">
         <v>332</v>
       </c>
-      <c r="G53" s="206" t="s">
+      <c r="G53" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H53" s="207">
+      <c r="H53" s="204">
         <v>296569917134.39996</v>
       </c>
-      <c r="I53" s="207">
+      <c r="I53" s="204">
         <v>296569917134.39996</v>
       </c>
-      <c r="J53" s="207">
+      <c r="J53" s="204">
         <v>605707205559</v>
       </c>
     </row>
     <row r="54" spans="2:10" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B54" s="252" t="s">
+      <c r="B54" s="249" t="s">
         <v>172</v>
       </c>
-      <c r="C54" s="201" t="s">
+      <c r="C54" s="198" t="s">
         <v>173</v>
       </c>
-      <c r="D54" s="202"/>
-      <c r="E54" s="194" t="s">
+      <c r="D54" s="199"/>
+      <c r="E54" s="191" t="s">
         <v>271</v>
       </c>
-      <c r="F54" s="211"/>
-      <c r="G54" s="195" t="s">
+      <c r="F54" s="208"/>
+      <c r="G54" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H54" s="196"/>
-      <c r="I54" s="196"/>
-      <c r="J54" s="196"/>
+      <c r="H54" s="193"/>
+      <c r="I54" s="193"/>
+      <c r="J54" s="193"/>
     </row>
     <row r="55" spans="2:10" ht="105" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B55" s="252" t="s">
+      <c r="B55" s="249" t="s">
         <v>195</v>
       </c>
-      <c r="C55" s="201" t="s">
+      <c r="C55" s="198" t="s">
         <v>194</v>
       </c>
-      <c r="D55" s="202" t="s">
+      <c r="D55" s="199" t="s">
         <v>291</v>
       </c>
-      <c r="E55" s="203" t="s">
+      <c r="E55" s="200" t="s">
         <v>328</v>
       </c>
-      <c r="F55" s="201" t="s">
+      <c r="F55" s="198" t="s">
         <v>334</v>
       </c>
-      <c r="G55" s="195" t="s">
+      <c r="G55" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H55" s="196">
+      <c r="H55" s="193">
         <v>2055600500</v>
       </c>
-      <c r="I55" s="196"/>
-      <c r="J55" s="196">
+      <c r="I55" s="193"/>
+      <c r="J55" s="193">
         <v>2055600500</v>
       </c>
     </row>
     <row r="56" spans="2:10" ht="105" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B56" s="252" t="s">
+      <c r="B56" s="249" t="s">
         <v>196</v>
       </c>
-      <c r="C56" s="201" t="s">
+      <c r="C56" s="198" t="s">
         <v>202</v>
       </c>
-      <c r="D56" s="202" t="s">
+      <c r="D56" s="199" t="s">
         <v>293</v>
       </c>
-      <c r="E56" s="203" t="s">
+      <c r="E56" s="200" t="s">
         <v>310</v>
       </c>
-      <c r="F56" s="201" t="s">
+      <c r="F56" s="198" t="s">
         <v>334</v>
       </c>
-      <c r="G56" s="195" t="s">
+      <c r="G56" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H56" s="196">
+      <c r="H56" s="193">
         <v>802444365238</v>
       </c>
-      <c r="I56" s="196"/>
-      <c r="J56" s="196">
+      <c r="I56" s="193"/>
+      <c r="J56" s="193">
         <v>802444365238</v>
       </c>
     </row>
     <row r="57" spans="2:10" ht="63" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B57" s="252" t="s">
+      <c r="B57" s="249" t="s">
         <v>197</v>
       </c>
-      <c r="C57" s="201" t="s">
+      <c r="C57" s="198" t="s">
         <v>248</v>
       </c>
-      <c r="D57" s="202" t="s">
+      <c r="D57" s="199" t="s">
         <v>305</v>
       </c>
-      <c r="E57" s="203" t="s">
+      <c r="E57" s="200" t="s">
         <v>273</v>
       </c>
-      <c r="F57" s="201" t="s">
+      <c r="F57" s="198" t="s">
         <v>332</v>
       </c>
-      <c r="G57" s="195" t="s">
+      <c r="G57" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H57" s="256">
+      <c r="H57" s="253">
         <v>650000000000</v>
       </c>
-      <c r="I57" s="257"/>
-      <c r="J57" s="196">
+      <c r="I57" s="254"/>
+      <c r="J57" s="193">
         <v>11300000000000</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="105" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B58" s="252" t="s">
+      <c r="B58" s="249" t="s">
         <v>247</v>
       </c>
-      <c r="C58" s="201" t="s">
+      <c r="C58" s="198" t="s">
         <v>220</v>
       </c>
-      <c r="D58" s="202" t="s">
+      <c r="D58" s="199" t="s">
         <v>294</v>
       </c>
-      <c r="E58" s="203" t="s">
+      <c r="E58" s="200" t="s">
         <v>329</v>
       </c>
-      <c r="F58" s="201" t="s">
+      <c r="F58" s="198" t="s">
         <v>334</v>
       </c>
-      <c r="G58" s="195" t="s">
+      <c r="G58" s="192" t="s">
         <v>176</v>
       </c>
-      <c r="H58" s="258"/>
-      <c r="I58" s="259"/>
-      <c r="J58" s="196"/>
+      <c r="H58" s="255"/>
+      <c r="I58" s="256"/>
+      <c r="J58" s="193"/>
     </row>
     <row r="59" spans="2:10" ht="84" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B59" s="241" t="s">
+      <c r="B59" s="238" t="s">
         <v>306</v>
       </c>
-      <c r="C59" s="201" t="s">
+      <c r="C59" s="198" t="s">
         <v>307</v>
       </c>
-      <c r="D59" s="202" t="s">
+      <c r="D59" s="199" t="s">
         <v>308</v>
       </c>
-      <c r="E59" s="194"/>
-      <c r="F59" s="211"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="196"/>
-      <c r="I59" s="196"/>
-      <c r="J59" s="196"/>
+      <c r="E59" s="191"/>
+      <c r="F59" s="208"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
     </row>
     <row r="60" spans="2:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B60" s="241"/>
-      <c r="C60" s="211"/>
-      <c r="D60" s="212"/>
-      <c r="E60" s="194"/>
-      <c r="F60" s="211"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="196"/>
-      <c r="I60" s="196"/>
-      <c r="J60" s="196"/>
+      <c r="B60" s="238"/>
+      <c r="C60" s="208"/>
+      <c r="D60" s="209"/>
+      <c r="E60" s="191"/>
+      <c r="F60" s="208"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
     </row>
     <row r="61" spans="2:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B61" s="241"/>
-      <c r="C61" s="211"/>
-      <c r="D61" s="212"/>
-      <c r="E61" s="194"/>
-      <c r="F61" s="211"/>
-      <c r="G61" s="195"/>
-      <c r="H61" s="196"/>
-      <c r="I61" s="196"/>
-      <c r="J61" s="196"/>
+      <c r="B61" s="238"/>
+      <c r="C61" s="208"/>
+      <c r="D61" s="209"/>
+      <c r="E61" s="191"/>
+      <c r="F61" s="208"/>
+      <c r="G61" s="192"/>
+      <c r="H61" s="193"/>
+      <c r="I61" s="193"/>
+      <c r="J61" s="193"/>
     </row>
     <row r="62" spans="2:10" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B62" s="241"/>
-      <c r="C62" s="211"/>
-      <c r="D62" s="212"/>
-      <c r="E62" s="194"/>
-      <c r="F62" s="211"/>
-      <c r="G62" s="195"/>
-      <c r="H62" s="196"/>
-      <c r="I62" s="196"/>
-      <c r="J62" s="196"/>
+      <c r="B62" s="238"/>
+      <c r="C62" s="208"/>
+      <c r="D62" s="209"/>
+      <c r="E62" s="191"/>
+      <c r="F62" s="208"/>
+      <c r="G62" s="192"/>
+      <c r="H62" s="193"/>
+      <c r="I62" s="193"/>
+      <c r="J62" s="193"/>
     </row>
     <row r="63" spans="2:10" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="240"/>
-      <c r="C63" s="216"/>
-      <c r="D63" s="217"/>
-      <c r="E63" s="204"/>
-      <c r="F63" s="216"/>
-      <c r="G63" s="205"/>
-      <c r="H63" s="184"/>
-      <c r="I63" s="184"/>
-      <c r="J63" s="184"/>
+      <c r="B63" s="237"/>
+      <c r="C63" s="213"/>
+      <c r="D63" s="214"/>
+      <c r="E63" s="201"/>
+      <c r="F63" s="213"/>
+      <c r="G63" s="202"/>
+      <c r="H63" s="181"/>
+      <c r="I63" s="181"/>
+      <c r="J63" s="181"/>
     </row>
     <row r="64" spans="2:10" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="250" t="s">
+      <c r="B64" s="247" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="218" t="s">
+      <c r="C64" s="215" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="219"/>
-      <c r="E64" s="199"/>
-      <c r="F64" s="220"/>
-      <c r="G64" s="200"/>
-      <c r="H64" s="189"/>
-      <c r="I64" s="189"/>
-      <c r="J64" s="189"/>
+      <c r="D64" s="216"/>
+      <c r="E64" s="196"/>
+      <c r="F64" s="217"/>
+      <c r="G64" s="197"/>
+      <c r="H64" s="186"/>
+      <c r="I64" s="186"/>
+      <c r="J64" s="186"/>
     </row>
     <row r="65" spans="1:11" ht="84" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B65" s="251" t="s">
+      <c r="B65" s="248" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="190" t="s">
+      <c r="C65" s="187" t="s">
         <v>0</v>
       </c>
-      <c r="D65" s="191" t="s">
+      <c r="D65" s="188" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="177" t="s">
+      <c r="E65" s="174" t="s">
         <v>279</v>
       </c>
-      <c r="F65" s="273" t="s">
+      <c r="F65" s="258" t="s">
         <v>334</v>
       </c>
-      <c r="G65" s="178"/>
-      <c r="H65" s="179">
+      <c r="G65" s="175"/>
+      <c r="H65" s="176">
         <v>3228738967724</v>
       </c>
-      <c r="I65" s="179"/>
-      <c r="J65" s="179">
+      <c r="I65" s="176"/>
+      <c r="J65" s="176">
         <v>3228738967724</v>
       </c>
     </row>
     <row r="66" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B66" s="252" t="s">
+      <c r="B66" s="249" t="s">
         <v>145</v>
       </c>
-      <c r="C66" s="192" t="s">
+      <c r="C66" s="189" t="s">
         <v>135</v>
       </c>
-      <c r="D66" s="193"/>
-      <c r="E66" s="194" t="s">
+      <c r="D66" s="190"/>
+      <c r="E66" s="191" t="s">
         <v>19</v>
       </c>
-      <c r="F66" s="211"/>
-      <c r="G66" s="195"/>
-      <c r="H66" s="196"/>
-      <c r="I66" s="196"/>
-      <c r="J66" s="196"/>
+      <c r="F66" s="208"/>
+      <c r="G66" s="192"/>
+      <c r="H66" s="193"/>
+      <c r="I66" s="193"/>
+      <c r="J66" s="193"/>
     </row>
     <row r="67" spans="1:11" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B67" s="252" t="s">
+      <c r="B67" s="249" t="s">
         <v>162</v>
       </c>
-      <c r="C67" s="192" t="s">
+      <c r="C67" s="189" t="s">
         <v>167</v>
       </c>
-      <c r="D67" s="193"/>
-      <c r="E67" s="194" t="s">
+      <c r="D67" s="190"/>
+      <c r="E67" s="191" t="s">
         <v>166</v>
       </c>
-      <c r="F67" s="211"/>
-      <c r="G67" s="195"/>
-      <c r="H67" s="196"/>
-      <c r="I67" s="196"/>
-      <c r="J67" s="196"/>
+      <c r="F67" s="208"/>
+      <c r="G67" s="192"/>
+      <c r="H67" s="193"/>
+      <c r="I67" s="193"/>
+      <c r="J67" s="193"/>
     </row>
     <row r="68" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B68" s="252"/>
-      <c r="C68" s="192" t="s">
+      <c r="B68" s="249"/>
+      <c r="C68" s="189" t="s">
         <v>187</v>
       </c>
-      <c r="D68" s="193"/>
-      <c r="E68" s="194" t="s">
+      <c r="D68" s="190"/>
+      <c r="E68" s="191" t="s">
         <v>189</v>
       </c>
-      <c r="F68" s="211"/>
-      <c r="G68" s="195"/>
-      <c r="H68" s="196"/>
-      <c r="I68" s="196"/>
-      <c r="J68" s="196"/>
+      <c r="F68" s="208"/>
+      <c r="G68" s="192"/>
+      <c r="H68" s="193"/>
+      <c r="I68" s="193"/>
+      <c r="J68" s="193"/>
     </row>
     <row r="69" spans="1:11" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B69" s="252"/>
-      <c r="C69" s="192" t="s">
+      <c r="B69" s="249"/>
+      <c r="C69" s="189" t="s">
         <v>204</v>
       </c>
-      <c r="D69" s="193"/>
-      <c r="E69" s="194" t="s">
+      <c r="D69" s="190"/>
+      <c r="E69" s="191" t="s">
         <v>205</v>
       </c>
-      <c r="F69" s="211"/>
-      <c r="G69" s="195"/>
-      <c r="H69" s="196"/>
-      <c r="I69" s="196"/>
-      <c r="J69" s="196"/>
+      <c r="F69" s="208"/>
+      <c r="G69" s="192"/>
+      <c r="H69" s="193"/>
+      <c r="I69" s="193"/>
+      <c r="J69" s="193"/>
     </row>
     <row r="70" spans="1:11" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B70" s="241"/>
-      <c r="C70" s="211" t="s">
+      <c r="B70" s="238"/>
+      <c r="C70" s="208" t="s">
         <v>85</v>
       </c>
-      <c r="D70" s="212"/>
-      <c r="E70" s="194" t="s">
+      <c r="D70" s="209"/>
+      <c r="E70" s="191" t="s">
         <v>86</v>
       </c>
-      <c r="F70" s="211"/>
-      <c r="G70" s="195"/>
-      <c r="H70" s="196"/>
-      <c r="I70" s="196"/>
-      <c r="J70" s="196"/>
+      <c r="F70" s="208"/>
+      <c r="G70" s="192"/>
+      <c r="H70" s="193"/>
+      <c r="I70" s="193"/>
+      <c r="J70" s="193"/>
     </row>
     <row r="71" spans="1:11" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B71" s="241"/>
-      <c r="C71" s="211" t="s">
+      <c r="B71" s="238"/>
+      <c r="C71" s="208" t="s">
         <v>63</v>
       </c>
-      <c r="D71" s="212"/>
-      <c r="E71" s="194" t="s">
+      <c r="D71" s="209"/>
+      <c r="E71" s="191" t="s">
         <v>87</v>
       </c>
-      <c r="F71" s="211"/>
-      <c r="G71" s="195"/>
-      <c r="H71" s="196"/>
-      <c r="I71" s="196"/>
-      <c r="J71" s="196"/>
+      <c r="F71" s="208"/>
+      <c r="G71" s="192"/>
+      <c r="H71" s="193"/>
+      <c r="I71" s="193"/>
+      <c r="J71" s="193"/>
     </row>
     <row r="72" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B72" s="241"/>
-      <c r="C72" s="211"/>
-      <c r="D72" s="212"/>
-      <c r="E72" s="194"/>
-      <c r="F72" s="211"/>
-      <c r="G72" s="195"/>
-      <c r="H72" s="196"/>
-      <c r="I72" s="196"/>
-      <c r="J72" s="196"/>
+      <c r="B72" s="238"/>
+      <c r="C72" s="208"/>
+      <c r="D72" s="209"/>
+      <c r="E72" s="191"/>
+      <c r="F72" s="208"/>
+      <c r="G72" s="192"/>
+      <c r="H72" s="193"/>
+      <c r="I72" s="193"/>
+      <c r="J72" s="193"/>
     </row>
     <row r="73" spans="1:11" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="241"/>
-      <c r="C73" s="211"/>
-      <c r="D73" s="212"/>
-      <c r="E73" s="194"/>
-      <c r="F73" s="211"/>
-      <c r="G73" s="195"/>
-      <c r="H73" s="196"/>
-      <c r="I73" s="196"/>
-      <c r="J73" s="196"/>
+      <c r="B73" s="238"/>
+      <c r="C73" s="208"/>
+      <c r="D73" s="209"/>
+      <c r="E73" s="191"/>
+      <c r="F73" s="208"/>
+      <c r="G73" s="192"/>
+      <c r="H73" s="193"/>
+      <c r="I73" s="193"/>
+      <c r="J73" s="193"/>
     </row>
     <row r="74" spans="1:11" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="135"/>
-      <c r="B74" s="250" t="s">
+      <c r="A74" s="132"/>
+      <c r="B74" s="247" t="s">
         <v>249</v>
       </c>
-      <c r="C74" s="220" t="s">
+      <c r="C74" s="217" t="s">
         <v>259</v>
       </c>
-      <c r="D74" s="221"/>
-      <c r="E74" s="199"/>
-      <c r="F74" s="220"/>
-      <c r="G74" s="200"/>
-      <c r="H74" s="189"/>
-      <c r="I74" s="189"/>
-      <c r="J74" s="189"/>
+      <c r="D74" s="218"/>
+      <c r="E74" s="196"/>
+      <c r="F74" s="217"/>
+      <c r="G74" s="197"/>
+      <c r="H74" s="186"/>
+      <c r="I74" s="186"/>
+      <c r="J74" s="186"/>
       <c r="K74" s="1" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="63" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B75" s="252" t="s">
+      <c r="B75" s="249" t="s">
         <v>250</v>
       </c>
-      <c r="C75" s="201" t="s">
+      <c r="C75" s="198" t="s">
         <v>207</v>
       </c>
-      <c r="D75" s="202" t="s">
+      <c r="D75" s="199" t="s">
         <v>301</v>
       </c>
-      <c r="E75" s="203" t="s">
+      <c r="E75" s="200" t="s">
         <v>260</v>
       </c>
-      <c r="F75" s="201" t="s">
+      <c r="F75" s="198" t="s">
         <v>334</v>
       </c>
-      <c r="G75" s="206" t="s">
+      <c r="G75" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H75" s="207">
+      <c r="H75" s="204">
         <v>235785343910</v>
       </c>
-      <c r="I75" s="207">
+      <c r="I75" s="204">
         <f>Table1[[#This Row],[بار مالی نهایی(ریال)
 (درصورت اخذ)]]</f>
         <v>86294058926</v>
       </c>
-      <c r="J75" s="207">
+      <c r="J75" s="204">
         <f>H75-K75</f>
         <v>86294058926</v>
       </c>
-      <c r="K75" s="107">
+      <c r="K75" s="104">
         <v>149491284984</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="63" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B76" s="252" t="s">
+      <c r="B76" s="249" t="s">
         <v>253</v>
       </c>
-      <c r="C76" s="201" t="s">
+      <c r="C76" s="198" t="s">
         <v>251</v>
       </c>
-      <c r="D76" s="202" t="s">
+      <c r="D76" s="199" t="s">
         <v>300</v>
       </c>
-      <c r="E76" s="203" t="s">
+      <c r="E76" s="200" t="s">
         <v>326</v>
       </c>
-      <c r="F76" s="201" t="s">
+      <c r="F76" s="198" t="s">
         <v>332</v>
       </c>
-      <c r="G76" s="206" t="s">
+      <c r="G76" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H76" s="207">
+      <c r="H76" s="204">
         <v>77992144113.279984</v>
       </c>
-      <c r="I76" s="196">
+      <c r="I76" s="193">
         <f>Table1[[#This Row],[بار مالی نهایی(ریال)
 (درصورت اخذ)]]</f>
         <v>42533404491.719978</v>
       </c>
-      <c r="J76" s="196">
+      <c r="J76" s="193">
         <f t="shared" ref="J76:J81" si="0">H76-K76</f>
         <v>42533404491.719978</v>
       </c>
-      <c r="K76" s="107">
+      <c r="K76" s="104">
         <v>35458739621.560005</v>
       </c>
     </row>
     <row r="77" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B77" s="252" t="s">
+      <c r="B77" s="249" t="s">
         <v>255</v>
       </c>
-      <c r="C77" s="201" t="s">
+      <c r="C77" s="198" t="s">
         <v>254</v>
       </c>
-      <c r="D77" s="202"/>
-      <c r="E77" s="203" t="s">
+      <c r="D77" s="199"/>
+      <c r="E77" s="200" t="s">
         <v>261</v>
       </c>
-      <c r="F77" s="201"/>
-      <c r="G77" s="206" t="s">
+      <c r="F77" s="198"/>
+      <c r="G77" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H77" s="207">
+      <c r="H77" s="204">
         <v>21442337280</v>
       </c>
-      <c r="I77" s="207">
+      <c r="I77" s="204">
         <f>Table1[[#This Row],[بار مالی نهایی(ریال)
 (درصورت اخذ)]]</f>
         <v>21442337280</v>
       </c>
-      <c r="J77" s="207">
+      <c r="J77" s="204">
         <f t="shared" si="0"/>
         <v>21442337280</v>
       </c>
-      <c r="K77" s="107">
+      <c r="K77" s="104">
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="63" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B78" s="252" t="s">
+      <c r="B78" s="249" t="s">
         <v>256</v>
       </c>
-      <c r="C78" s="201" t="s">
+      <c r="C78" s="198" t="s">
         <v>252</v>
       </c>
-      <c r="D78" s="202" t="s">
+      <c r="D78" s="199" t="s">
         <v>299</v>
       </c>
-      <c r="E78" s="203" t="s">
+      <c r="E78" s="200" t="s">
         <v>264</v>
       </c>
-      <c r="F78" s="201" t="s">
+      <c r="F78" s="198" t="s">
         <v>332</v>
       </c>
-      <c r="G78" s="206" t="s">
+      <c r="G78" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H78" s="207">
+      <c r="H78" s="204">
         <v>31834405680</v>
       </c>
-      <c r="I78" s="196">
+      <c r="I78" s="193">
         <f>Table1[[#This Row],[بار مالی نهایی(ریال)
 (درصورت اخذ)]]</f>
         <v>14058506935</v>
       </c>
-      <c r="J78" s="196">
+      <c r="J78" s="193">
         <f t="shared" si="0"/>
         <v>14058506935</v>
       </c>
-      <c r="K78" s="107">
+      <c r="K78" s="104">
         <v>17775898745</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="105" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B79" s="252" t="s">
+      <c r="B79" s="249" t="s">
         <v>257</v>
       </c>
-      <c r="C79" s="201" t="s">
+      <c r="C79" s="198" t="s">
         <v>265</v>
       </c>
-      <c r="D79" s="202" t="s">
+      <c r="D79" s="199" t="s">
         <v>298</v>
       </c>
-      <c r="E79" s="203" t="s">
+      <c r="E79" s="200" t="s">
         <v>312</v>
       </c>
-      <c r="F79" s="201"/>
-      <c r="G79" s="206" t="s">
+      <c r="F79" s="198"/>
+      <c r="G79" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H79" s="207">
+      <c r="H79" s="204">
         <v>1314358925000</v>
       </c>
-      <c r="I79" s="196">
+      <c r="I79" s="193">
         <f>Table1[[#This Row],[بار مالی نهایی(ریال)
 (درصورت اخذ)]]</f>
         <v>1314358925000</v>
       </c>
-      <c r="J79" s="196">
+      <c r="J79" s="193">
         <f t="shared" si="0"/>
         <v>1314358925000</v>
       </c>
@@ -5509,335 +5500,335 @@
       </c>
     </row>
     <row r="80" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B80" s="252" t="s">
+      <c r="B80" s="249" t="s">
         <v>258</v>
       </c>
-      <c r="C80" s="201" t="s">
+      <c r="C80" s="198" t="s">
         <v>246</v>
       </c>
-      <c r="D80" s="202" t="s">
+      <c r="D80" s="199" t="s">
         <v>296</v>
       </c>
-      <c r="E80" s="203" t="s">
+      <c r="E80" s="200" t="s">
         <v>266</v>
       </c>
-      <c r="F80" s="201"/>
-      <c r="G80" s="206" t="s">
+      <c r="F80" s="198"/>
+      <c r="G80" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H80" s="207">
+      <c r="H80" s="204">
         <v>9505104750</v>
       </c>
-      <c r="I80" s="207">
+      <c r="I80" s="204">
         <f>Table1[[#This Row],[بار مالی نهایی(ریال)
 (درصورت اخذ)]]</f>
         <v>9505104750</v>
       </c>
-      <c r="J80" s="207">
+      <c r="J80" s="204">
         <f t="shared" si="0"/>
         <v>9505104750</v>
       </c>
-      <c r="K80" s="107">
+      <c r="K80" s="104">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="63" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B81" s="252" t="s">
+      <c r="B81" s="249" t="s">
         <v>263</v>
       </c>
-      <c r="C81" s="201" t="s">
+      <c r="C81" s="198" t="s">
         <v>262</v>
       </c>
-      <c r="D81" s="202" t="s">
+      <c r="D81" s="199" t="s">
         <v>297</v>
       </c>
-      <c r="E81" s="203" t="s">
+      <c r="E81" s="200" t="s">
         <v>276</v>
       </c>
-      <c r="F81" s="201" t="s">
+      <c r="F81" s="198" t="s">
         <v>334</v>
       </c>
-      <c r="G81" s="206" t="s">
+      <c r="G81" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H81" s="207">
+      <c r="H81" s="204">
         <v>75816773333</v>
       </c>
-      <c r="I81" s="196">
+      <c r="I81" s="193">
         <f>Table1[[#This Row],[بار مالی نهایی(ریال)
 (درصورت اخذ)]]</f>
         <v>70690153233</v>
       </c>
-      <c r="J81" s="196">
+      <c r="J81" s="193">
         <f t="shared" si="0"/>
         <v>70690153233</v>
       </c>
-      <c r="K81" s="107">
+      <c r="K81" s="104">
         <v>5126620100</v>
       </c>
     </row>
     <row r="82" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B82" s="241"/>
-      <c r="C82" s="211"/>
-      <c r="D82" s="212"/>
-      <c r="E82" s="194"/>
-      <c r="F82" s="211"/>
-      <c r="G82" s="195"/>
-      <c r="H82" s="196"/>
-      <c r="I82" s="196"/>
-      <c r="J82" s="196"/>
+      <c r="B82" s="238"/>
+      <c r="C82" s="208"/>
+      <c r="D82" s="209"/>
+      <c r="E82" s="191"/>
+      <c r="F82" s="208"/>
+      <c r="G82" s="192"/>
+      <c r="H82" s="193"/>
+      <c r="I82" s="193"/>
+      <c r="J82" s="193"/>
     </row>
     <row r="83" spans="1:11" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="240"/>
-      <c r="C83" s="216"/>
-      <c r="D83" s="217"/>
-      <c r="E83" s="204"/>
-      <c r="F83" s="216"/>
-      <c r="G83" s="205"/>
-      <c r="H83" s="184"/>
-      <c r="I83" s="184"/>
-      <c r="J83" s="184"/>
+      <c r="B83" s="237"/>
+      <c r="C83" s="213"/>
+      <c r="D83" s="214"/>
+      <c r="E83" s="201"/>
+      <c r="F83" s="213"/>
+      <c r="G83" s="202"/>
+      <c r="H83" s="181"/>
+      <c r="I83" s="181"/>
+      <c r="J83" s="181"/>
     </row>
     <row r="84" spans="1:11" ht="26.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="135"/>
-      <c r="B84" s="250" t="s">
+      <c r="A84" s="132"/>
+      <c r="B84" s="247" t="s">
         <v>126</v>
       </c>
-      <c r="C84" s="220" t="s">
+      <c r="C84" s="217" t="s">
         <v>35</v>
       </c>
-      <c r="D84" s="221"/>
-      <c r="E84" s="199"/>
-      <c r="F84" s="220"/>
-      <c r="G84" s="200"/>
-      <c r="H84" s="189"/>
-      <c r="I84" s="189"/>
-      <c r="J84" s="189"/>
+      <c r="D84" s="218"/>
+      <c r="E84" s="196"/>
+      <c r="F84" s="217"/>
+      <c r="G84" s="197"/>
+      <c r="H84" s="186"/>
+      <c r="I84" s="186"/>
+      <c r="J84" s="186"/>
     </row>
     <row r="85" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B85" s="251" t="s">
+      <c r="B85" s="248" t="s">
         <v>163</v>
       </c>
-      <c r="C85" s="190" t="s">
+      <c r="C85" s="187" t="s">
         <v>10</v>
       </c>
-      <c r="D85" s="191"/>
-      <c r="E85" s="208" t="s">
+      <c r="D85" s="188"/>
+      <c r="E85" s="205" t="s">
         <v>303</v>
       </c>
-      <c r="F85" s="190"/>
-      <c r="G85" s="209" t="s">
+      <c r="F85" s="187"/>
+      <c r="G85" s="206" t="s">
         <v>176</v>
       </c>
-      <c r="H85" s="210"/>
-      <c r="I85" s="210"/>
-      <c r="J85" s="210"/>
+      <c r="H85" s="207"/>
+      <c r="I85" s="207"/>
+      <c r="J85" s="207"/>
     </row>
     <row r="86" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B86" s="252" t="s">
+      <c r="B86" s="249" t="s">
         <v>164</v>
       </c>
-      <c r="C86" s="201" t="s">
+      <c r="C86" s="198" t="s">
         <v>130</v>
       </c>
-      <c r="D86" s="202"/>
-      <c r="E86" s="203" t="s">
+      <c r="D86" s="199"/>
+      <c r="E86" s="200" t="s">
         <v>131</v>
       </c>
-      <c r="F86" s="201"/>
-      <c r="G86" s="206" t="s">
+      <c r="F86" s="198"/>
+      <c r="G86" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H86" s="207"/>
-      <c r="I86" s="207"/>
-      <c r="J86" s="207"/>
+      <c r="H86" s="204"/>
+      <c r="I86" s="204"/>
+      <c r="J86" s="204"/>
     </row>
     <row r="87" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B87" s="252" t="s">
+      <c r="B87" s="249" t="s">
         <v>165</v>
       </c>
-      <c r="C87" s="201" t="s">
+      <c r="C87" s="198" t="s">
         <v>132</v>
       </c>
-      <c r="D87" s="202"/>
-      <c r="E87" s="203" t="s">
+      <c r="D87" s="199"/>
+      <c r="E87" s="200" t="s">
         <v>133</v>
       </c>
-      <c r="F87" s="201"/>
-      <c r="G87" s="206" t="s">
+      <c r="F87" s="198"/>
+      <c r="G87" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H87" s="207"/>
-      <c r="I87" s="207"/>
-      <c r="J87" s="207"/>
+      <c r="H87" s="204"/>
+      <c r="I87" s="204"/>
+      <c r="J87" s="204"/>
     </row>
     <row r="88" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B88" s="252" t="s">
+      <c r="B88" s="249" t="s">
         <v>177</v>
       </c>
-      <c r="C88" s="201" t="s">
+      <c r="C88" s="198" t="s">
         <v>178</v>
       </c>
-      <c r="D88" s="202"/>
-      <c r="E88" s="203" t="s">
+      <c r="D88" s="199"/>
+      <c r="E88" s="200" t="s">
         <v>190</v>
       </c>
-      <c r="F88" s="201"/>
-      <c r="G88" s="206" t="s">
+      <c r="F88" s="198"/>
+      <c r="G88" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H88" s="207"/>
-      <c r="I88" s="207"/>
-      <c r="J88" s="207"/>
+      <c r="H88" s="204"/>
+      <c r="I88" s="204"/>
+      <c r="J88" s="204"/>
     </row>
     <row r="89" spans="1:11" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B89" s="241"/>
-      <c r="C89" s="201" t="s">
+      <c r="B89" s="238"/>
+      <c r="C89" s="198" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="202"/>
-      <c r="E89" s="203" t="s">
+      <c r="D89" s="199"/>
+      <c r="E89" s="200" t="s">
         <v>16</v>
       </c>
-      <c r="F89" s="201"/>
-      <c r="G89" s="206" t="s">
+      <c r="F89" s="198"/>
+      <c r="G89" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H89" s="207"/>
-      <c r="I89" s="207"/>
-      <c r="J89" s="207"/>
+      <c r="H89" s="204"/>
+      <c r="I89" s="204"/>
+      <c r="J89" s="204"/>
     </row>
     <row r="90" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B90" s="252" t="s">
+      <c r="B90" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="C90" s="192" t="s">
+      <c r="C90" s="189" t="s">
         <v>201</v>
       </c>
-      <c r="D90" s="193"/>
-      <c r="E90" s="223"/>
-      <c r="F90" s="192"/>
-      <c r="G90" s="222"/>
-      <c r="H90" s="224"/>
-      <c r="I90" s="224"/>
-      <c r="J90" s="224"/>
+      <c r="D90" s="190"/>
+      <c r="E90" s="220"/>
+      <c r="F90" s="189"/>
+      <c r="G90" s="219"/>
+      <c r="H90" s="221"/>
+      <c r="I90" s="221"/>
+      <c r="J90" s="221"/>
     </row>
     <row r="91" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B91" s="252" t="s">
+      <c r="B91" s="249" t="s">
         <v>206</v>
       </c>
-      <c r="C91" s="201" t="s">
+      <c r="C91" s="198" t="s">
         <v>217</v>
       </c>
-      <c r="D91" s="202"/>
-      <c r="E91" s="203" t="s">
+      <c r="D91" s="199"/>
+      <c r="E91" s="200" t="s">
         <v>218</v>
       </c>
-      <c r="F91" s="201"/>
-      <c r="G91" s="206" t="s">
+      <c r="F91" s="198"/>
+      <c r="G91" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H91" s="207"/>
-      <c r="I91" s="207"/>
-      <c r="J91" s="207"/>
-      <c r="K91" s="107"/>
+      <c r="H91" s="204"/>
+      <c r="I91" s="204"/>
+      <c r="J91" s="204"/>
+      <c r="K91" s="104"/>
     </row>
     <row r="92" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B92" s="252" t="s">
+      <c r="B92" s="249" t="s">
         <v>210</v>
       </c>
-      <c r="C92" s="201" t="s">
+      <c r="C92" s="198" t="s">
         <v>313</v>
       </c>
-      <c r="D92" s="202"/>
-      <c r="E92" s="203" t="s">
+      <c r="D92" s="199"/>
+      <c r="E92" s="200" t="s">
         <v>315</v>
       </c>
-      <c r="F92" s="201"/>
-      <c r="G92" s="206"/>
-      <c r="H92" s="207"/>
-      <c r="I92" s="207"/>
-      <c r="J92" s="207"/>
+      <c r="F92" s="198"/>
+      <c r="G92" s="203"/>
+      <c r="H92" s="204"/>
+      <c r="I92" s="204"/>
+      <c r="J92" s="204"/>
     </row>
     <row r="93" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B93" s="252" t="s">
+      <c r="B93" s="249" t="s">
         <v>216</v>
       </c>
-      <c r="C93" s="201" t="s">
+      <c r="C93" s="198" t="s">
         <v>314</v>
       </c>
-      <c r="D93" s="202"/>
-      <c r="E93" s="203" t="s">
+      <c r="D93" s="199"/>
+      <c r="E93" s="200" t="s">
         <v>316</v>
       </c>
-      <c r="F93" s="201"/>
-      <c r="G93" s="206" t="s">
+      <c r="F93" s="198"/>
+      <c r="G93" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H93" s="207"/>
-      <c r="I93" s="207"/>
-      <c r="J93" s="207"/>
+      <c r="H93" s="204"/>
+      <c r="I93" s="204"/>
+      <c r="J93" s="204"/>
     </row>
     <row r="94" spans="1:11" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B94" s="252" t="s">
+      <c r="B94" s="249" t="s">
         <v>221</v>
       </c>
-      <c r="C94" s="201" t="s">
+      <c r="C94" s="198" t="s">
         <v>319</v>
       </c>
-      <c r="D94" s="202"/>
-      <c r="E94" s="203" t="s">
+      <c r="D94" s="199"/>
+      <c r="E94" s="200" t="s">
         <v>320</v>
       </c>
-      <c r="F94" s="201"/>
-      <c r="G94" s="206" t="s">
+      <c r="F94" s="198"/>
+      <c r="G94" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H94" s="207"/>
-      <c r="I94" s="207"/>
-      <c r="J94" s="207"/>
+      <c r="H94" s="204"/>
+      <c r="I94" s="204"/>
+      <c r="J94" s="204"/>
     </row>
     <row r="95" spans="1:11" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B95" s="252" t="s">
+      <c r="B95" s="249" t="s">
         <v>231</v>
       </c>
-      <c r="C95" s="201" t="s">
+      <c r="C95" s="198" t="s">
         <v>324</v>
       </c>
-      <c r="D95" s="202"/>
-      <c r="E95" s="203" t="s">
+      <c r="D95" s="199"/>
+      <c r="E95" s="200" t="s">
         <v>321</v>
       </c>
-      <c r="F95" s="201"/>
-      <c r="G95" s="206" t="s">
+      <c r="F95" s="198"/>
+      <c r="G95" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H95" s="207"/>
-      <c r="I95" s="207"/>
-      <c r="J95" s="207"/>
+      <c r="H95" s="204"/>
+      <c r="I95" s="204"/>
+      <c r="J95" s="204"/>
     </row>
     <row r="96" spans="1:11" ht="23.25" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="135"/>
-      <c r="B96" s="255" t="s">
+      <c r="A96" s="132"/>
+      <c r="B96" s="252" t="s">
         <v>318</v>
       </c>
-      <c r="C96" s="236" t="s">
+      <c r="C96" s="233" t="s">
         <v>322</v>
       </c>
-      <c r="D96" s="237"/>
-      <c r="E96" s="238" t="s">
+      <c r="D96" s="234"/>
+      <c r="E96" s="235" t="s">
         <v>323</v>
       </c>
-      <c r="F96" s="276"/>
-      <c r="G96" s="206" t="s">
+      <c r="F96" s="261"/>
+      <c r="G96" s="203" t="s">
         <v>176</v>
       </c>
-      <c r="H96" s="239"/>
-      <c r="I96" s="239"/>
-      <c r="J96" s="239"/>
+      <c r="H96" s="236"/>
+      <c r="I96" s="236"/>
+      <c r="J96" s="236"/>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B97" s="138"/>
+      <c r="B97" s="135"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B43:J63">
@@ -5933,734 +5924,734 @@
   <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="45" outlineLevelRow="2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="143" customWidth="1"/>
-    <col min="2" max="2" width="41.28515625" style="169" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.140625" style="166" customWidth="1"/>
-    <col min="4" max="4" width="79.7109375" style="166" customWidth="1"/>
-    <col min="5" max="5" width="255.5703125" style="167" customWidth="1"/>
-    <col min="6" max="6" width="23.140625" style="167" customWidth="1"/>
-    <col min="7" max="7" width="62.7109375" style="168" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="83.28515625" style="168" customWidth="1"/>
-    <col min="10" max="10" width="37.7109375" style="142" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" style="142" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" style="142" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="142"/>
+    <col min="1" max="1" width="4.85546875" style="140" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" style="166" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.140625" style="163" customWidth="1"/>
+    <col min="4" max="4" width="79.7109375" style="163" customWidth="1"/>
+    <col min="5" max="5" width="255.5703125" style="164" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" style="164" customWidth="1"/>
+    <col min="7" max="7" width="62.7109375" style="165" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="83.28515625" style="165" customWidth="1"/>
+    <col min="10" max="10" width="37.7109375" style="139" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" style="139" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="139" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="139"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="140" customFormat="1" ht="111.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="262"/>
-      <c r="B1" s="264" t="s">
+    <row r="1" spans="1:12" s="137" customFormat="1" ht="111.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="264"/>
+      <c r="B1" s="266" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="266" t="s">
+      <c r="C1" s="268" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="266" t="s">
+      <c r="D1" s="268" t="s">
         <v>284</v>
       </c>
-      <c r="E1" s="264" t="s">
+      <c r="E1" s="266" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="266" t="s">
+      <c r="F1" s="268" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="139" t="s">
+      <c r="G1" s="136" t="s">
         <v>280</v>
       </c>
-      <c r="H1" s="139" t="s">
+      <c r="H1" s="136" t="s">
         <v>281</v>
       </c>
-      <c r="I1" s="139" t="s">
+      <c r="I1" s="136" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="140" customFormat="1" ht="45.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="263"/>
-      <c r="B2" s="265"/>
-      <c r="C2" s="267"/>
-      <c r="D2" s="267"/>
-      <c r="E2" s="265"/>
-      <c r="F2" s="267"/>
-      <c r="G2" s="141">
+    <row r="2" spans="1:12" s="137" customFormat="1" ht="45.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="265"/>
+      <c r="B2" s="267"/>
+      <c r="C2" s="269"/>
+      <c r="D2" s="269"/>
+      <c r="E2" s="267"/>
+      <c r="F2" s="269"/>
+      <c r="G2" s="138">
         <f>SUM(G3:G30)</f>
         <v>5912017713923.4561</v>
       </c>
-      <c r="H2" s="141">
+      <c r="H2" s="138">
         <f>SUM(H3:H30)</f>
         <v>758257989741.19995</v>
       </c>
-      <c r="I2" s="141">
+      <c r="I2" s="138">
         <f>SUM(I3:I30)</f>
         <v>28400087092584.602</v>
       </c>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="142"/>
-    </row>
-    <row r="3" spans="1:12" s="140" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="143"/>
-      <c r="B3" s="232" t="s">
+      <c r="J2" s="139"/>
+      <c r="K2" s="139"/>
+      <c r="L2" s="139"/>
+    </row>
+    <row r="3" spans="1:12" s="137" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="140"/>
+      <c r="B3" s="229" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="144" t="s">
+      <c r="C3" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="225"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="142"/>
-    </row>
-    <row r="4" spans="1:12" s="140" customFormat="1" ht="45.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="143"/>
-      <c r="B4" s="233" t="s">
+      <c r="D3" s="222"/>
+      <c r="E3" s="142"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="144"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="139"/>
+      <c r="K3" s="139"/>
+      <c r="L3" s="139"/>
+    </row>
+    <row r="4" spans="1:12" s="137" customFormat="1" ht="45.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="140"/>
+      <c r="B4" s="230" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="148" t="s">
+      <c r="C4" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="226"/>
-      <c r="E4" s="149" t="s">
+      <c r="D4" s="223"/>
+      <c r="E4" s="146" t="s">
         <v>282</v>
       </c>
-      <c r="F4" s="150"/>
-      <c r="G4" s="151"/>
-      <c r="H4" s="151"/>
-      <c r="I4" s="151">
+      <c r="F4" s="147"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148">
         <f>H4</f>
         <v>0</v>
       </c>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142"/>
-    </row>
-    <row r="5" spans="1:12" s="140" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="143"/>
-      <c r="B5" s="232" t="s">
+      <c r="J4" s="139"/>
+      <c r="K4" s="139"/>
+      <c r="L4" s="139"/>
+    </row>
+    <row r="5" spans="1:12" s="137" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="140"/>
+      <c r="B5" s="229" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="225"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
-      <c r="L5" s="142"/>
-    </row>
-    <row r="6" spans="1:12" s="140" customFormat="1" ht="135.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="143"/>
-      <c r="B6" s="234" t="s">
+      <c r="D5" s="222"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="150"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
+      <c r="L5" s="139"/>
+    </row>
+    <row r="6" spans="1:12" s="137" customFormat="1" ht="135.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="140"/>
+      <c r="B6" s="231" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="154" t="s">
+      <c r="C6" s="151" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="227" t="s">
+      <c r="D6" s="224" t="s">
         <v>286</v>
       </c>
-      <c r="E6" s="155" t="s">
+      <c r="E6" s="152" t="s">
         <v>274</v>
       </c>
-      <c r="F6" s="156" t="s">
+      <c r="F6" s="153" t="s">
         <v>176</v>
       </c>
-      <c r="G6" s="157">
+      <c r="G6" s="154">
         <v>134402080225</v>
       </c>
-      <c r="H6" s="157">
+      <c r="H6" s="154">
         <f>G6*0.7</f>
         <v>94081456157.5</v>
       </c>
-      <c r="I6" s="157">
+      <c r="I6" s="154">
         <v>134402080225</v>
       </c>
-      <c r="J6" s="142"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="142"/>
-    </row>
-    <row r="7" spans="1:12" s="140" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="143"/>
-      <c r="B7" s="232" t="s">
+      <c r="J6" s="139"/>
+      <c r="K6" s="139"/>
+      <c r="L6" s="139"/>
+    </row>
+    <row r="7" spans="1:12" s="137" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="140"/>
+      <c r="B7" s="229" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="144" t="s">
+      <c r="C7" s="141" t="s">
         <v>193</v>
       </c>
-      <c r="D7" s="225"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="147"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="142"/>
-      <c r="K7" s="142"/>
-      <c r="L7" s="142"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="149"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
     </row>
     <row r="8" spans="1:12" ht="90" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B8" s="234" t="s">
+      <c r="B8" s="231" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="158" t="s">
+      <c r="C8" s="155" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="227" t="s">
+      <c r="D8" s="224" t="s">
         <v>286</v>
       </c>
-      <c r="E8" s="155" t="s">
+      <c r="E8" s="152" t="s">
         <v>234</v>
       </c>
-      <c r="F8" s="156" t="s">
+      <c r="F8" s="153" t="s">
         <v>176</v>
       </c>
-      <c r="G8" s="157">
+      <c r="G8" s="154">
         <f>35779531251*1.3</f>
         <v>46513390626.300003</v>
       </c>
-      <c r="H8" s="157">
+      <c r="H8" s="154">
         <v>46513390626.300003</v>
       </c>
-      <c r="I8" s="157">
+      <c r="I8" s="154">
         <f>H8</f>
         <v>46513390626.300003</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="234" t="s">
+      <c r="B9" s="231" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="158" t="s">
+      <c r="C9" s="155" t="s">
         <v>239</v>
       </c>
-      <c r="D9" s="228"/>
-      <c r="E9" s="155" t="s">
+      <c r="D9" s="225"/>
+      <c r="E9" s="152" t="s">
         <v>240</v>
       </c>
-      <c r="F9" s="156" t="s">
+      <c r="F9" s="153" t="s">
         <v>176</v>
       </c>
-      <c r="G9" s="157">
+      <c r="G9" s="154">
         <v>107200000000</v>
       </c>
-      <c r="H9" s="157">
+      <c r="H9" s="154">
         <v>107200000000</v>
       </c>
-      <c r="I9" s="157">
+      <c r="I9" s="154">
         <f>H9</f>
         <v>107200000000</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="232" t="s">
+      <c r="B10" s="229" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="225"/>
-      <c r="E10" s="152"/>
-      <c r="F10" s="153"/>
-      <c r="G10" s="147"/>
-      <c r="H10" s="147"/>
-      <c r="I10" s="147"/>
+      <c r="D10" s="222"/>
+      <c r="E10" s="149"/>
+      <c r="F10" s="150"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="144"/>
     </row>
     <row r="11" spans="1:12" ht="270" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B11" s="234" t="s">
+      <c r="B11" s="231" t="s">
         <v>147</v>
       </c>
-      <c r="C11" s="227" t="s">
+      <c r="C11" s="224" t="s">
         <v>140</v>
       </c>
-      <c r="D11" s="227" t="s">
+      <c r="D11" s="224" t="s">
         <v>285</v>
       </c>
-      <c r="E11" s="159" t="s">
+      <c r="E11" s="156" t="s">
         <v>245</v>
       </c>
-      <c r="F11" s="160" t="s">
+      <c r="F11" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="G11" s="161"/>
-      <c r="H11" s="161"/>
-      <c r="I11" s="161">
+      <c r="G11" s="158"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="158">
         <f t="shared" ref="I11:I16" si="0">H11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="270" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B12" s="234" t="s">
+      <c r="B12" s="231" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="227" t="s">
+      <c r="C12" s="224" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="227" t="s">
+      <c r="D12" s="224" t="s">
         <v>285</v>
       </c>
-      <c r="E12" s="159" t="s">
+      <c r="E12" s="156" t="s">
         <v>245</v>
       </c>
-      <c r="F12" s="160" t="s">
+      <c r="F12" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="G12" s="161"/>
-      <c r="H12" s="161"/>
-      <c r="I12" s="161">
+      <c r="G12" s="158"/>
+      <c r="H12" s="158"/>
+      <c r="I12" s="158">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B13" s="234" t="s">
+      <c r="B13" s="231" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="154" t="s">
+      <c r="C13" s="151" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="227" t="s">
+      <c r="D13" s="224" t="s">
         <v>287</v>
       </c>
-      <c r="E13" s="159" t="s">
+      <c r="E13" s="156" t="s">
         <v>181</v>
       </c>
-      <c r="F13" s="160"/>
-      <c r="G13" s="161"/>
-      <c r="H13" s="161"/>
-      <c r="I13" s="161">
+      <c r="F13" s="157"/>
+      <c r="G13" s="158"/>
+      <c r="H13" s="158"/>
+      <c r="I13" s="158">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="135" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B14" s="234" t="s">
+      <c r="B14" s="231" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="227" t="s">
+      <c r="C14" s="224" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="227" t="s">
+      <c r="D14" s="224" t="s">
         <v>291</v>
       </c>
-      <c r="E14" s="159" t="s">
+      <c r="E14" s="156" t="s">
         <v>275</v>
       </c>
-      <c r="F14" s="160" t="s">
+      <c r="F14" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="G14" s="161"/>
-      <c r="H14" s="161"/>
-      <c r="I14" s="161">
+      <c r="G14" s="158"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="158">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="90" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B15" s="234" t="s">
+      <c r="B15" s="231" t="s">
         <v>236</v>
       </c>
-      <c r="C15" s="154" t="s">
+      <c r="C15" s="151" t="s">
         <v>237</v>
       </c>
-      <c r="D15" s="228"/>
-      <c r="E15" s="155" t="s">
+      <c r="D15" s="225"/>
+      <c r="E15" s="152" t="s">
         <v>238</v>
       </c>
-      <c r="F15" s="156" t="s">
+      <c r="F15" s="153" t="s">
         <v>176</v>
       </c>
-      <c r="G15" s="157">
+      <c r="G15" s="154">
         <v>35000000000</v>
       </c>
-      <c r="H15" s="157">
+      <c r="H15" s="154">
         <v>35000000000</v>
       </c>
-      <c r="I15" s="157">
+      <c r="I15" s="154">
         <f t="shared" si="0"/>
         <v>35000000000</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="90.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="235"/>
-      <c r="C16" s="162" t="s">
+      <c r="B16" s="232"/>
+      <c r="C16" s="159" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="229"/>
-      <c r="E16" s="155" t="s">
+      <c r="D16" s="226"/>
+      <c r="E16" s="152" t="s">
         <v>278</v>
       </c>
-      <c r="F16" s="160"/>
-      <c r="G16" s="161"/>
-      <c r="H16" s="161"/>
-      <c r="I16" s="161">
+      <c r="F16" s="157"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="140" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="143"/>
-      <c r="B17" s="232" t="s">
+    <row r="17" spans="1:12" s="137" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="140"/>
+      <c r="B17" s="229" t="s">
         <v>137</v>
       </c>
-      <c r="C17" s="144" t="s">
+      <c r="C17" s="141" t="s">
         <v>138</v>
       </c>
-      <c r="D17" s="225"/>
-      <c r="E17" s="152"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="147"/>
-      <c r="H17" s="147"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="142"/>
-      <c r="K17" s="142"/>
-      <c r="L17" s="142"/>
-    </row>
-    <row r="18" spans="1:12" s="140" customFormat="1" ht="90.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="143"/>
-      <c r="B18" s="234" t="s">
+      <c r="D17" s="222"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="150"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="144"/>
+      <c r="J17" s="139"/>
+      <c r="K17" s="139"/>
+      <c r="L17" s="139"/>
+    </row>
+    <row r="18" spans="1:12" s="137" customFormat="1" ht="90.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="140"/>
+      <c r="B18" s="231" t="s">
         <v>156</v>
       </c>
-      <c r="C18" s="158" t="s">
+      <c r="C18" s="155" t="s">
         <v>139</v>
       </c>
-      <c r="D18" s="227" t="s">
+      <c r="D18" s="224" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="155" t="s">
+      <c r="E18" s="152" t="s">
         <v>233</v>
       </c>
-      <c r="F18" s="156" t="s">
+      <c r="F18" s="153" t="s">
         <v>176</v>
       </c>
-      <c r="G18" s="157">
+      <c r="G18" s="154">
         <f>953385000*1.3</f>
         <v>1239400500</v>
       </c>
-      <c r="H18" s="157">
+      <c r="H18" s="154">
         <f>G18</f>
         <v>1239400500</v>
       </c>
-      <c r="I18" s="157">
+      <c r="I18" s="154">
         <f>H18</f>
         <v>1239400500</v>
       </c>
-      <c r="J18" s="142"/>
-      <c r="K18" s="142"/>
-      <c r="L18" s="142"/>
-    </row>
-    <row r="19" spans="1:12" s="140" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="143"/>
-      <c r="B19" s="232" t="s">
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+    </row>
+    <row r="19" spans="1:12" s="137" customFormat="1" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="140"/>
+      <c r="B19" s="229" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="144" t="s">
+      <c r="C19" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="225"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="153"/>
-      <c r="G19" s="147"/>
-      <c r="H19" s="147"/>
-      <c r="I19" s="147"/>
-      <c r="J19" s="142"/>
-      <c r="K19" s="142"/>
-      <c r="L19" s="142"/>
-    </row>
-    <row r="20" spans="1:12" s="140" customFormat="1" ht="360" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A20" s="143"/>
-      <c r="B20" s="233" t="s">
+      <c r="D19" s="222"/>
+      <c r="E19" s="149"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="144"/>
+      <c r="H19" s="144"/>
+      <c r="I19" s="144"/>
+      <c r="J19" s="139"/>
+      <c r="K19" s="139"/>
+      <c r="L19" s="139"/>
+    </row>
+    <row r="20" spans="1:12" s="137" customFormat="1" ht="360" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A20" s="140"/>
+      <c r="B20" s="230" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="227" t="s">
+      <c r="C20" s="224" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="230" t="s">
+      <c r="D20" s="227" t="s">
         <v>288</v>
       </c>
-      <c r="E20" s="163" t="s">
+      <c r="E20" s="160" t="s">
         <v>267</v>
       </c>
-      <c r="F20" s="150" t="s">
+      <c r="F20" s="147" t="s">
         <v>176</v>
       </c>
-      <c r="G20" s="151">
+      <c r="G20" s="148">
         <f>(189284772+402438295+188275870+2006147434)*1.3</f>
         <v>3621990282.3000002</v>
       </c>
-      <c r="H20" s="151"/>
-      <c r="I20" s="151">
+      <c r="H20" s="148"/>
+      <c r="I20" s="148">
         <v>3621990282.3000002</v>
       </c>
-      <c r="J20" s="142"/>
-      <c r="K20" s="142"/>
-      <c r="L20" s="142"/>
-    </row>
-    <row r="21" spans="1:12" s="140" customFormat="1" ht="360" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A21" s="143"/>
-      <c r="B21" s="234" t="s">
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+    </row>
+    <row r="21" spans="1:12" s="137" customFormat="1" ht="360" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A21" s="140"/>
+      <c r="B21" s="231" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="227" t="s">
+      <c r="C21" s="224" t="s">
         <v>269</v>
       </c>
-      <c r="D21" s="230" t="s">
+      <c r="D21" s="227" t="s">
         <v>289</v>
       </c>
-      <c r="E21" s="155" t="s">
+      <c r="E21" s="152" t="s">
         <v>317</v>
       </c>
-      <c r="F21" s="160" t="s">
+      <c r="F21" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="G21" s="161">
+      <c r="G21" s="158">
         <f>735415334655.456</f>
         <v>735415334655.45605</v>
       </c>
-      <c r="H21" s="161">
+      <c r="H21" s="158">
         <v>177653825323</v>
       </c>
-      <c r="I21" s="161">
+      <c r="I21" s="158">
         <f>7265308780621-2800961355729</f>
         <v>4464347424892</v>
       </c>
-      <c r="J21" s="142"/>
-      <c r="K21" s="142"/>
-      <c r="L21" s="142"/>
-    </row>
-    <row r="22" spans="1:12" s="140" customFormat="1" ht="409.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A22" s="143"/>
-      <c r="B22" s="234" t="s">
+      <c r="J21" s="139"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="139"/>
+    </row>
+    <row r="22" spans="1:12" s="137" customFormat="1" ht="409.5" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A22" s="140"/>
+      <c r="B22" s="231" t="s">
         <v>160</v>
       </c>
-      <c r="C22" s="227" t="s">
+      <c r="C22" s="224" t="s">
         <v>136</v>
       </c>
-      <c r="D22" s="227" t="s">
+      <c r="D22" s="224" t="s">
         <v>290</v>
       </c>
-      <c r="E22" s="155" t="s">
+      <c r="E22" s="152" t="s">
         <v>268</v>
       </c>
-      <c r="F22" s="160" t="s">
+      <c r="F22" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="G22" s="161">
+      <c r="G22" s="158">
         <v>4400000000000</v>
       </c>
-      <c r="H22" s="161"/>
-      <c r="I22" s="161">
+      <c r="H22" s="158"/>
+      <c r="I22" s="158">
         <v>23000000000000</v>
       </c>
-      <c r="J22" s="142"/>
-      <c r="K22" s="142"/>
-      <c r="L22" s="142"/>
-    </row>
-    <row r="23" spans="1:12" s="140" customFormat="1" ht="90" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A23" s="143"/>
-      <c r="B23" s="234" t="s">
+      <c r="J22" s="139"/>
+      <c r="K22" s="139"/>
+      <c r="L22" s="139"/>
+    </row>
+    <row r="23" spans="1:12" s="137" customFormat="1" ht="90" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A23" s="140"/>
+      <c r="B23" s="231" t="s">
         <v>169</v>
       </c>
-      <c r="C23" s="154" t="s">
+      <c r="C23" s="151" t="s">
         <v>270</v>
       </c>
-      <c r="D23" s="228"/>
-      <c r="E23" s="155" t="s">
+      <c r="D23" s="225"/>
+      <c r="E23" s="152" t="s">
         <v>283</v>
       </c>
-      <c r="F23" s="156" t="s">
+      <c r="F23" s="153" t="s">
         <v>176</v>
       </c>
-      <c r="G23" s="157">
+      <c r="G23" s="154">
         <v>296569917134.39996</v>
       </c>
-      <c r="H23" s="157">
+      <c r="H23" s="154">
         <v>296569917134.39996</v>
       </c>
-      <c r="I23" s="157">
+      <c r="I23" s="154">
         <v>605707205559</v>
       </c>
-      <c r="J23" s="142"/>
-      <c r="K23" s="142"/>
-      <c r="L23" s="142"/>
-    </row>
-    <row r="24" spans="1:12" s="140" customFormat="1" ht="225" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A24" s="143"/>
-      <c r="B24" s="234" t="s">
+      <c r="J23" s="139"/>
+      <c r="K23" s="139"/>
+      <c r="L23" s="139"/>
+    </row>
+    <row r="24" spans="1:12" s="137" customFormat="1" ht="225" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A24" s="140"/>
+      <c r="B24" s="231" t="s">
         <v>195</v>
       </c>
-      <c r="C24" s="227" t="s">
+      <c r="C24" s="224" t="s">
         <v>194</v>
       </c>
-      <c r="D24" s="227" t="s">
+      <c r="D24" s="224" t="s">
         <v>291</v>
       </c>
-      <c r="E24" s="155" t="s">
+      <c r="E24" s="152" t="s">
         <v>272</v>
       </c>
-      <c r="F24" s="160" t="s">
+      <c r="F24" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="G24" s="161">
+      <c r="G24" s="158">
         <v>2055600500</v>
       </c>
-      <c r="H24" s="161"/>
-      <c r="I24" s="161">
+      <c r="H24" s="158"/>
+      <c r="I24" s="158">
         <v>2055600500</v>
       </c>
-      <c r="J24" s="142"/>
-      <c r="K24" s="142"/>
-      <c r="L24" s="142"/>
-    </row>
-    <row r="25" spans="1:12" s="140" customFormat="1" ht="225" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A25" s="143"/>
-      <c r="B25" s="234" t="s">
+      <c r="J24" s="139"/>
+      <c r="K24" s="139"/>
+      <c r="L24" s="139"/>
+    </row>
+    <row r="25" spans="1:12" s="137" customFormat="1" ht="225" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A25" s="140"/>
+      <c r="B25" s="231" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="227" t="s">
+      <c r="C25" s="224" t="s">
         <v>292</v>
       </c>
-      <c r="D25" s="227" t="s">
+      <c r="D25" s="224" t="s">
         <v>293</v>
       </c>
-      <c r="E25" s="155" t="s">
+      <c r="E25" s="152" t="s">
         <v>310</v>
       </c>
-      <c r="F25" s="160" t="s">
+      <c r="F25" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="G25" s="161"/>
-      <c r="H25" s="161"/>
-      <c r="I25" s="161"/>
-      <c r="J25" s="142"/>
-      <c r="K25" s="142"/>
-      <c r="L25" s="142"/>
-    </row>
-    <row r="26" spans="1:12" s="140" customFormat="1" ht="135" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A26" s="143"/>
-      <c r="B26" s="234" t="s">
+      <c r="G25" s="158"/>
+      <c r="H25" s="158"/>
+      <c r="I25" s="158"/>
+      <c r="J25" s="139"/>
+      <c r="K25" s="139"/>
+      <c r="L25" s="139"/>
+    </row>
+    <row r="26" spans="1:12" s="137" customFormat="1" ht="135" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A26" s="140"/>
+      <c r="B26" s="231" t="s">
         <v>197</v>
       </c>
-      <c r="C26" s="227" t="s">
+      <c r="C26" s="224" t="s">
         <v>248</v>
       </c>
-      <c r="D26" s="227" t="s">
+      <c r="D26" s="224" t="s">
         <v>304</v>
       </c>
-      <c r="E26" s="155" t="s">
+      <c r="E26" s="152" t="s">
         <v>273</v>
       </c>
-      <c r="F26" s="160" t="s">
+      <c r="F26" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="G26" s="161">
+      <c r="G26" s="158">
         <v>150000000000</v>
       </c>
-      <c r="H26" s="161"/>
-      <c r="I26" s="161">
+      <c r="H26" s="158"/>
+      <c r="I26" s="158">
         <v>0</v>
       </c>
-      <c r="J26" s="142"/>
-      <c r="K26" s="142"/>
-      <c r="L26" s="142"/>
-    </row>
-    <row r="27" spans="1:12" s="140" customFormat="1" ht="225" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A27" s="143"/>
-      <c r="B27" s="234" t="s">
+      <c r="J26" s="139"/>
+      <c r="K26" s="139"/>
+      <c r="L26" s="139"/>
+    </row>
+    <row r="27" spans="1:12" s="137" customFormat="1" ht="225" outlineLevel="2" x14ac:dyDescent="0.25">
+      <c r="A27" s="140"/>
+      <c r="B27" s="231" t="s">
         <v>247</v>
       </c>
-      <c r="C27" s="227" t="s">
+      <c r="C27" s="224" t="s">
         <v>220</v>
       </c>
-      <c r="D27" s="230" t="s">
+      <c r="D27" s="227" t="s">
         <v>294</v>
       </c>
-      <c r="E27" s="155" t="s">
+      <c r="E27" s="152" t="s">
         <v>311</v>
       </c>
-      <c r="F27" s="160" t="s">
+      <c r="F27" s="157" t="s">
         <v>176</v>
       </c>
-      <c r="G27" s="161"/>
-      <c r="H27" s="161"/>
-      <c r="I27" s="161">
+      <c r="G27" s="158"/>
+      <c r="H27" s="158"/>
+      <c r="I27" s="158">
         <f t="shared" ref="I27" si="1">H27</f>
         <v>0</v>
       </c>
-      <c r="J27" s="142"/>
-      <c r="K27" s="142"/>
-      <c r="L27" s="142"/>
-    </row>
-    <row r="28" spans="1:12" s="117" customFormat="1" ht="180.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="134"/>
-      <c r="B28" s="235" t="s">
+      <c r="J27" s="139"/>
+      <c r="K27" s="139"/>
+      <c r="L27" s="139"/>
+    </row>
+    <row r="28" spans="1:12" s="114" customFormat="1" ht="180.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="131"/>
+      <c r="B28" s="232" t="s">
         <v>306</v>
       </c>
-      <c r="C28" s="154" t="s">
+      <c r="C28" s="151" t="s">
         <v>307</v>
       </c>
-      <c r="D28" s="230" t="s">
+      <c r="D28" s="227" t="s">
         <v>308</v>
       </c>
-      <c r="E28" s="155" t="s">
+      <c r="E28" s="152" t="s">
         <v>309</v>
       </c>
-      <c r="F28" s="195"/>
-      <c r="G28" s="196"/>
-      <c r="H28" s="161"/>
+      <c r="F28" s="192"/>
+      <c r="G28" s="193"/>
+      <c r="H28" s="158"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:12" ht="56.25" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="229" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="164" t="s">
+      <c r="C29" s="161" t="s">
         <v>125</v>
       </c>
-      <c r="D29" s="231"/>
-      <c r="E29" s="152"/>
-      <c r="F29" s="153"/>
-      <c r="G29" s="147"/>
-      <c r="H29" s="147"/>
-      <c r="I29" s="147"/>
+      <c r="D29" s="228"/>
+      <c r="E29" s="149"/>
+      <c r="F29" s="150"/>
+      <c r="G29" s="144"/>
+      <c r="H29" s="144"/>
+      <c r="I29" s="144"/>
     </row>
     <row r="30" spans="1:12" ht="135" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="B30" s="233" t="s">
+      <c r="B30" s="230" t="s">
         <v>144</v>
       </c>
-      <c r="C30" s="148" t="s">
+      <c r="C30" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="227" t="s">
+      <c r="D30" s="224" t="s">
         <v>295</v>
       </c>
-      <c r="E30" s="149" t="s">
+      <c r="E30" s="146" t="s">
         <v>279</v>
       </c>
-      <c r="F30" s="150"/>
-      <c r="G30" s="151"/>
-      <c r="H30" s="151"/>
-      <c r="I30" s="151"/>
-    </row>
-    <row r="31" spans="1:12" s="140" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="143"/>
-      <c r="B31" s="165"/>
-      <c r="C31" s="166"/>
-      <c r="D31" s="166"/>
-      <c r="E31" s="167"/>
-      <c r="F31" s="167"/>
-      <c r="G31" s="168"/>
-      <c r="H31" s="168"/>
-      <c r="I31" s="168"/>
-      <c r="J31" s="142"/>
-      <c r="K31" s="142"/>
-      <c r="L31" s="142"/>
+      <c r="F30" s="147"/>
+      <c r="G30" s="148"/>
+      <c r="H30" s="148"/>
+      <c r="I30" s="148"/>
+    </row>
+    <row r="31" spans="1:12" s="137" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="140"/>
+      <c r="B31" s="162"/>
+      <c r="C31" s="163"/>
+      <c r="D31" s="163"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="165"/>
+      <c r="H31" s="165"/>
+      <c r="I31" s="165"/>
+      <c r="J31" s="139"/>
+      <c r="K31" s="139"/>
+      <c r="L31" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6746,7 +6737,7 @@
   <dimension ref="A1:H113"/>
   <sheetFormatPr defaultRowHeight="22.5" outlineLevelRow="2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="117" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" style="114" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" style="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50.140625" style="56" customWidth="1"/>
     <col min="4" max="4" width="99.42578125" style="56" customWidth="1"/>
@@ -6754,18 +6745,18 @@
     <col min="6" max="6" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="37.7109375" style="117" customWidth="1"/>
-    <col min="10" max="10" width="20.5703125" style="117" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" style="117" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="117"/>
+    <col min="9" max="9" width="37.7109375" style="114" customWidth="1"/>
+    <col min="10" max="10" width="20.5703125" style="114" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" style="114" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="114"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="109"/>
+      <c r="A1" s="106"/>
       <c r="B1" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="105" t="s">
         <v>36</v>
       </c>
       <c r="D1" s="75" t="s">
@@ -6774,19 +6765,19 @@
       <c r="E1" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="106" t="s">
+      <c r="F1" s="103" t="s">
         <v>214</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="103" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.5" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="115"/>
+      <c r="A2" s="112"/>
       <c r="B2" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="113" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="55"/>
@@ -6801,8 +6792,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A3" s="115"/>
-      <c r="B3" s="104" t="s">
+      <c r="A3" s="112"/>
+      <c r="B3" s="101" t="s">
         <v>213</v>
       </c>
       <c r="C3" s="77" t="s">
@@ -6819,7 +6810,7 @@
       <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A4" s="115"/>
+      <c r="A4" s="112"/>
       <c r="B4" s="34"/>
       <c r="C4" s="76"/>
       <c r="D4" s="33"/>
@@ -6828,21 +6819,21 @@
       <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="115"/>
+      <c r="A5" s="112"/>
       <c r="B5" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="118"/>
+      <c r="D5" s="115"/>
       <c r="E5" s="59"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A6" s="115"/>
-      <c r="B6" s="104" t="s">
+      <c r="A6" s="112"/>
+      <c r="B6" s="101" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="77" t="s">
@@ -6856,8 +6847,8 @@
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A7" s="115"/>
-      <c r="B7" s="104" t="s">
+      <c r="A7" s="112"/>
+      <c r="B7" s="101" t="s">
         <v>120</v>
       </c>
       <c r="C7" s="78" t="s">
@@ -6871,7 +6862,7 @@
       <c r="G7" s="40"/>
     </row>
     <row r="8" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A8" s="115"/>
+      <c r="A8" s="112"/>
       <c r="B8" s="34"/>
       <c r="C8" s="79"/>
       <c r="D8" s="48"/>
@@ -6880,21 +6871,21 @@
       <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="115"/>
+      <c r="A9" s="112"/>
       <c r="B9" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="116" t="s">
+      <c r="C9" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="116"/>
+      <c r="D9" s="113"/>
       <c r="E9" s="63"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A10" s="115"/>
-      <c r="B10" s="104" t="s">
+      <c r="A10" s="112"/>
+      <c r="B10" s="101" t="s">
         <v>114</v>
       </c>
       <c r="C10" s="77" t="s">
@@ -6908,8 +6899,8 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A11" s="115"/>
-      <c r="B11" s="104" t="s">
+      <c r="A11" s="112"/>
+      <c r="B11" s="101" t="s">
         <v>115</v>
       </c>
       <c r="C11" s="80" t="s">
@@ -6929,8 +6920,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A12" s="115"/>
-      <c r="B12" s="104" t="s">
+      <c r="A12" s="112"/>
+      <c r="B12" s="101" t="s">
         <v>227</v>
       </c>
       <c r="C12" s="82" t="s">
@@ -6944,7 +6935,7 @@
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A13" s="115"/>
+      <c r="A13" s="112"/>
       <c r="B13" s="34"/>
       <c r="C13" s="79"/>
       <c r="D13" s="50"/>
@@ -6953,21 +6944,21 @@
       <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="115"/>
+      <c r="A14" s="112"/>
       <c r="B14" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="116" t="s">
+      <c r="C14" s="113" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="116"/>
+      <c r="D14" s="113"/>
       <c r="E14" s="63"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A15" s="115"/>
-      <c r="B15" s="104" t="s">
+      <c r="A15" s="112"/>
+      <c r="B15" s="101" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="77" t="s">
@@ -6981,8 +6972,8 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A16" s="115"/>
-      <c r="B16" s="104" t="s">
+      <c r="A16" s="112"/>
+      <c r="B16" s="101" t="s">
         <v>150</v>
       </c>
       <c r="C16" s="83" t="s">
@@ -7003,8 +6994,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A17" s="115"/>
-      <c r="B17" s="104" t="s">
+      <c r="A17" s="112"/>
+      <c r="B17" s="101" t="s">
         <v>151</v>
       </c>
       <c r="C17" s="81" t="s">
@@ -7013,7 +7004,7 @@
       <c r="D17" s="45" t="s">
         <v>240</v>
       </c>
-      <c r="E17" s="110" t="s">
+      <c r="E17" s="107" t="s">
         <v>176</v>
       </c>
       <c r="F17" s="99">
@@ -7024,8 +7015,8 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A18" s="115"/>
-      <c r="B18" s="104" t="s">
+      <c r="A18" s="112"/>
+      <c r="B18" s="101" t="s">
         <v>152</v>
       </c>
       <c r="C18" s="80"/>
@@ -7035,8 +7026,8 @@
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A19" s="115"/>
-      <c r="B19" s="104" t="s">
+      <c r="A19" s="112"/>
+      <c r="B19" s="101" t="s">
         <v>153</v>
       </c>
       <c r="C19" s="80" t="s">
@@ -7050,8 +7041,8 @@
       <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A20" s="115"/>
-      <c r="B20" s="104" t="s">
+      <c r="A20" s="112"/>
+      <c r="B20" s="101" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="80" t="s">
@@ -7065,8 +7056,8 @@
       <c r="G20" s="10"/>
     </row>
     <row r="21" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A21" s="115"/>
-      <c r="B21" s="104" t="s">
+      <c r="A21" s="112"/>
+      <c r="B21" s="101" t="s">
         <v>155</v>
       </c>
       <c r="C21" s="80" t="s">
@@ -7080,7 +7071,7 @@
       <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A22" s="115"/>
+      <c r="A22" s="112"/>
       <c r="B22" s="34"/>
       <c r="C22" s="79"/>
       <c r="D22" s="48"/>
@@ -7089,37 +7080,37 @@
       <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:8" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="115"/>
+      <c r="A23" s="112"/>
       <c r="B23" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="116" t="s">
+      <c r="C23" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="116"/>
+      <c r="D23" s="113"/>
       <c r="E23" s="63"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:8" ht="112.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A24" s="115"/>
+      <c r="A24" s="112"/>
       <c r="B24" s="44" t="s">
         <v>146</v>
       </c>
       <c r="C24" s="84" t="s">
         <v>129</v>
       </c>
-      <c r="D24" s="129" t="s">
+      <c r="D24" s="126" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="130" t="s">
+      <c r="E24" s="127" t="s">
         <v>176</v>
       </c>
-      <c r="F24" s="131"/>
-      <c r="G24" s="131"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
     </row>
     <row r="25" spans="1:8" ht="157.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A25" s="115"/>
+      <c r="A25" s="112"/>
       <c r="B25" s="44" t="s">
         <v>147</v>
       </c>
@@ -7139,7 +7130,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="157.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A26" s="115"/>
+      <c r="A26" s="112"/>
       <c r="B26" s="44" t="s">
         <v>148</v>
       </c>
@@ -7156,7 +7147,7 @@
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A27" s="115"/>
+      <c r="A27" s="112"/>
       <c r="B27" s="44" t="s">
         <v>183</v>
       </c>
@@ -7171,7 +7162,7 @@
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:8" ht="67.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A28" s="115"/>
+      <c r="A28" s="112"/>
       <c r="B28" s="44" t="s">
         <v>184</v>
       </c>
@@ -7188,7 +7179,7 @@
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A29" s="115"/>
+      <c r="A29" s="112"/>
       <c r="B29" s="44" t="s">
         <v>185</v>
       </c>
@@ -7203,7 +7194,7 @@
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A30" s="115"/>
+      <c r="A30" s="112"/>
       <c r="B30" s="44" t="s">
         <v>236</v>
       </c>
@@ -7224,7 +7215,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A31" s="115"/>
+      <c r="A31" s="112"/>
       <c r="B31" s="34"/>
       <c r="C31" s="85" t="s">
         <v>5</v>
@@ -7237,7 +7228,7 @@
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A32" s="115"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="34"/>
       <c r="C32" s="85" t="s">
         <v>6</v>
@@ -7250,7 +7241,7 @@
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A33" s="115"/>
+      <c r="A33" s="112"/>
       <c r="B33" s="34"/>
       <c r="C33" s="85" t="s">
         <v>7</v>
@@ -7263,7 +7254,7 @@
       <c r="G33" s="10"/>
     </row>
     <row r="34" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A34" s="115"/>
+      <c r="A34" s="112"/>
       <c r="B34" s="34"/>
       <c r="C34" s="85" t="s">
         <v>8</v>
@@ -7276,7 +7267,7 @@
       <c r="G34" s="10"/>
     </row>
     <row r="35" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A35" s="115"/>
+      <c r="A35" s="112"/>
       <c r="B35" s="34"/>
       <c r="C35" s="85" t="s">
         <v>1</v>
@@ -7289,7 +7280,7 @@
       <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A36" s="115"/>
+      <c r="A36" s="112"/>
       <c r="B36" s="34"/>
       <c r="C36" s="86" t="s">
         <v>25</v>
@@ -7302,7 +7293,7 @@
       <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A37" s="115"/>
+      <c r="A37" s="112"/>
       <c r="B37" s="34"/>
       <c r="C37" s="87"/>
       <c r="D37" s="50"/>
@@ -7311,20 +7302,20 @@
       <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="115"/>
+      <c r="A38" s="112"/>
       <c r="B38" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="C38" s="116" t="s">
+      <c r="C38" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="116"/>
+      <c r="D38" s="113"/>
       <c r="E38" s="63"/>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
     </row>
     <row r="39" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A39" s="115"/>
+      <c r="A39" s="112"/>
       <c r="B39" s="34"/>
       <c r="C39" s="88" t="s">
         <v>9</v>
@@ -7337,7 +7328,7 @@
       <c r="G39" s="7"/>
     </row>
     <row r="40" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A40" s="115"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="34"/>
       <c r="C40" s="89"/>
       <c r="D40" s="51"/>
@@ -7346,20 +7337,20 @@
       <c r="G40" s="41"/>
     </row>
     <row r="41" spans="1:7" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="115"/>
+      <c r="A41" s="112"/>
       <c r="B41" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="119" t="s">
+      <c r="C41" s="116" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="116"/>
+      <c r="D41" s="113"/>
       <c r="E41" s="63"/>
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
     </row>
     <row r="42" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A42" s="115"/>
+      <c r="A42" s="112"/>
       <c r="B42" s="44" t="s">
         <v>156</v>
       </c>
@@ -7382,20 +7373,20 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="115"/>
+      <c r="A43" s="112"/>
       <c r="B43" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="119" t="s">
+      <c r="C43" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="D43" s="116"/>
+      <c r="D43" s="113"/>
       <c r="E43" s="63"/>
       <c r="F43" s="9"/>
       <c r="G43" s="9"/>
     </row>
     <row r="44" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A44" s="115"/>
+      <c r="A44" s="112"/>
       <c r="B44" s="44" t="s">
         <v>157</v>
       </c>
@@ -7410,20 +7401,20 @@
       <c r="G44" s="11"/>
     </row>
     <row r="45" spans="1:7" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="115"/>
+      <c r="A45" s="112"/>
       <c r="B45" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="C45" s="119" t="s">
+      <c r="C45" s="116" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="116"/>
+      <c r="D45" s="113"/>
       <c r="E45" s="63"/>
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
     </row>
     <row r="46" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A46" s="115"/>
+      <c r="A46" s="112"/>
       <c r="B46" s="34"/>
       <c r="C46" s="91" t="s">
         <v>98</v>
@@ -7436,7 +7427,7 @@
       <c r="G46" s="32"/>
     </row>
     <row r="47" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A47" s="115"/>
+      <c r="A47" s="112"/>
       <c r="B47" s="34"/>
       <c r="C47" s="92" t="s">
         <v>64</v>
@@ -7449,27 +7440,27 @@
       <c r="G47" s="31"/>
     </row>
     <row r="48" spans="1:7" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="115"/>
+      <c r="A48" s="112"/>
       <c r="B48" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="C48" s="120" t="s">
+      <c r="C48" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="116"/>
+      <c r="D48" s="113"/>
       <c r="E48" s="63"/>
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
     </row>
     <row r="49" spans="1:7" ht="112.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A49" s="115"/>
+      <c r="A49" s="112"/>
       <c r="B49" s="44" t="s">
         <v>158</v>
       </c>
       <c r="C49" s="84" t="s">
         <v>128</v>
       </c>
-      <c r="D49" s="128" t="s">
+      <c r="D49" s="125" t="s">
         <v>229</v>
       </c>
       <c r="E49" s="71" t="s">
@@ -7481,7 +7472,7 @@
       <c r="G49" s="35"/>
     </row>
     <row r="50" spans="1:7" ht="157.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A50" s="115"/>
+      <c r="A50" s="112"/>
       <c r="B50" s="44" t="s">
         <v>159</v>
       </c>
@@ -7502,7 +7493,7 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="202.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A51" s="115"/>
+      <c r="A51" s="112"/>
       <c r="B51" s="44" t="s">
         <v>160</v>
       </c>
@@ -7521,7 +7512,7 @@
       <c r="G51" s="10"/>
     </row>
     <row r="52" spans="1:7" ht="90" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A52" s="115"/>
+      <c r="A52" s="112"/>
       <c r="B52" s="44" t="s">
         <v>161</v>
       </c>
@@ -7542,7 +7533,7 @@
       </c>
     </row>
     <row r="53" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A53" s="115"/>
+      <c r="A53" s="112"/>
       <c r="B53" s="44" t="s">
         <v>169</v>
       </c>
@@ -7555,7 +7546,7 @@
       <c r="E53" s="74" t="s">
         <v>176</v>
       </c>
-      <c r="F53" s="105">
+      <c r="F53" s="102">
         <v>677874096307.19995</v>
       </c>
       <c r="G53" s="99">
@@ -7564,7 +7555,7 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A54" s="115"/>
+      <c r="A54" s="112"/>
       <c r="B54" s="44" t="s">
         <v>172</v>
       </c>
@@ -7583,7 +7574,7 @@
       <c r="G54" s="10"/>
     </row>
     <row r="55" spans="1:7" ht="90" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A55" s="115"/>
+      <c r="A55" s="112"/>
       <c r="B55" s="44" t="s">
         <v>195</v>
       </c>
@@ -7600,7 +7591,7 @@
       <c r="G55" s="10"/>
     </row>
     <row r="56" spans="1:7" ht="67.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A56" s="115"/>
+      <c r="A56" s="112"/>
       <c r="B56" s="44" t="s">
         <v>196</v>
       </c>
@@ -7617,7 +7608,7 @@
       <c r="G56" s="10"/>
     </row>
     <row r="57" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A57" s="115"/>
+      <c r="A57" s="112"/>
       <c r="B57" s="44" t="s">
         <v>197</v>
       </c>
@@ -7632,7 +7623,7 @@
       <c r="G57" s="10"/>
     </row>
     <row r="58" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A58" s="115"/>
+      <c r="A58" s="112"/>
       <c r="B58" s="44" t="s">
         <v>219</v>
       </c>
@@ -7649,18 +7640,18 @@
       <c r="G58" s="10"/>
     </row>
     <row r="59" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A59" s="115"/>
-      <c r="B59" s="104"/>
+      <c r="A59" s="112"/>
+      <c r="B59" s="101"/>
       <c r="C59" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="D59" s="101"/>
-      <c r="E59" s="102"/>
-      <c r="F59" s="103"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="10"/>
       <c r="G59" s="10"/>
     </row>
     <row r="60" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A60" s="115"/>
+      <c r="A60" s="112"/>
       <c r="B60" s="34"/>
       <c r="C60" s="85" t="s">
         <v>44</v>
@@ -7673,7 +7664,7 @@
       <c r="G60" s="10"/>
     </row>
     <row r="61" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A61" s="115"/>
+      <c r="A61" s="112"/>
       <c r="B61" s="34"/>
       <c r="C61" s="93" t="s">
         <v>102</v>
@@ -7686,7 +7677,7 @@
       <c r="G61" s="13"/>
     </row>
     <row r="62" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A62" s="115"/>
+      <c r="A62" s="112"/>
       <c r="B62" s="34"/>
       <c r="C62" s="93" t="s">
         <v>104</v>
@@ -7699,7 +7690,7 @@
       <c r="G62" s="13"/>
     </row>
     <row r="63" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A63" s="115"/>
+      <c r="A63" s="112"/>
       <c r="B63" s="34"/>
       <c r="C63" s="93" t="s">
         <v>98</v>
@@ -7712,7 +7703,7 @@
       <c r="G63" s="13"/>
     </row>
     <row r="64" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A64" s="115"/>
+      <c r="A64" s="112"/>
       <c r="B64" s="34"/>
       <c r="C64" s="85" t="s">
         <v>76</v>
@@ -7725,7 +7716,7 @@
       <c r="G64" s="10"/>
     </row>
     <row r="65" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A65" s="115"/>
+      <c r="A65" s="112"/>
       <c r="B65" s="34"/>
       <c r="C65" s="85" t="s">
         <v>70</v>
@@ -7738,7 +7729,7 @@
       <c r="G65" s="10"/>
     </row>
     <row r="66" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A66" s="115"/>
+      <c r="A66" s="112"/>
       <c r="B66" s="34"/>
       <c r="C66" s="85" t="s">
         <v>43</v>
@@ -7751,7 +7742,7 @@
       <c r="G66" s="10"/>
     </row>
     <row r="67" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A67" s="115"/>
+      <c r="A67" s="112"/>
       <c r="B67" s="34"/>
       <c r="C67" s="85" t="s">
         <v>41</v>
@@ -7764,7 +7755,7 @@
       <c r="G67" s="10"/>
     </row>
     <row r="68" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A68" s="115"/>
+      <c r="A68" s="112"/>
       <c r="B68" s="34"/>
       <c r="C68" s="85" t="s">
         <v>68</v>
@@ -7777,7 +7768,7 @@
       <c r="G68" s="10"/>
     </row>
     <row r="69" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A69" s="115"/>
+      <c r="A69" s="112"/>
       <c r="B69" s="34"/>
       <c r="C69" s="85" t="s">
         <v>4</v>
@@ -7790,7 +7781,7 @@
       <c r="G69" s="10"/>
     </row>
     <row r="70" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A70" s="115"/>
+      <c r="A70" s="112"/>
       <c r="B70" s="34"/>
       <c r="C70" s="85" t="s">
         <v>49</v>
@@ -7803,7 +7794,7 @@
       <c r="G70" s="10"/>
     </row>
     <row r="71" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A71" s="115"/>
+      <c r="A71" s="112"/>
       <c r="B71" s="34"/>
       <c r="C71" s="86" t="s">
         <v>54</v>
@@ -7816,7 +7807,7 @@
       <c r="G71" s="16"/>
     </row>
     <row r="72" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A72" s="115"/>
+      <c r="A72" s="112"/>
       <c r="B72" s="34"/>
       <c r="C72" s="86" t="s">
         <v>61</v>
@@ -7829,7 +7820,7 @@
       <c r="G72" s="16"/>
     </row>
     <row r="73" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A73" s="115"/>
+      <c r="A73" s="112"/>
       <c r="B73" s="34"/>
       <c r="C73" s="86" t="s">
         <v>72</v>
@@ -7840,7 +7831,7 @@
       <c r="G73" s="16"/>
     </row>
     <row r="74" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A74" s="115"/>
+      <c r="A74" s="112"/>
       <c r="B74" s="34"/>
       <c r="C74" s="86" t="s">
         <v>77</v>
@@ -7853,7 +7844,7 @@
       <c r="G74" s="16"/>
     </row>
     <row r="75" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A75" s="115"/>
+      <c r="A75" s="112"/>
       <c r="B75" s="34"/>
       <c r="C75" s="94" t="s">
         <v>73</v>
@@ -7866,7 +7857,7 @@
       <c r="G75" s="16"/>
     </row>
     <row r="76" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A76" s="115"/>
+      <c r="A76" s="112"/>
       <c r="B76" s="34"/>
       <c r="C76" s="94" t="s">
         <v>83</v>
@@ -7879,7 +7870,7 @@
       <c r="G76" s="16"/>
     </row>
     <row r="77" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A77" s="115"/>
+      <c r="A77" s="112"/>
       <c r="B77" s="34"/>
       <c r="C77" s="94" t="s">
         <v>81</v>
@@ -7892,7 +7883,7 @@
       <c r="G77" s="16"/>
     </row>
     <row r="78" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A78" s="115"/>
+      <c r="A78" s="112"/>
       <c r="B78" s="34"/>
       <c r="C78" s="94" t="s">
         <v>96</v>
@@ -7905,7 +7896,7 @@
       <c r="G78" s="16"/>
     </row>
     <row r="79" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A79" s="115"/>
+      <c r="A79" s="112"/>
       <c r="B79" s="34"/>
       <c r="C79" s="86" t="s">
         <v>79</v>
@@ -7918,7 +7909,7 @@
       <c r="G79" s="16"/>
     </row>
     <row r="80" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A80" s="115"/>
+      <c r="A80" s="112"/>
       <c r="B80" s="34"/>
       <c r="C80" s="86" t="s">
         <v>56</v>
@@ -7931,7 +7922,7 @@
       <c r="G80" s="16"/>
     </row>
     <row r="81" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A81" s="115"/>
+      <c r="A81" s="112"/>
       <c r="B81" s="34"/>
       <c r="C81" s="87"/>
       <c r="D81" s="50"/>
@@ -7940,20 +7931,20 @@
       <c r="G81" s="8"/>
     </row>
     <row r="82" spans="1:7" ht="30" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="115"/>
+      <c r="A82" s="112"/>
       <c r="B82" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="C82" s="121" t="s">
+      <c r="C82" s="118" t="s">
         <v>125</v>
       </c>
-      <c r="D82" s="116"/>
+      <c r="D82" s="113"/>
       <c r="E82" s="63"/>
       <c r="F82" s="9"/>
       <c r="G82" s="9"/>
     </row>
     <row r="83" spans="1:7" ht="67.5" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A83" s="115"/>
+      <c r="A83" s="112"/>
       <c r="B83" s="44" t="s">
         <v>144</v>
       </c>
@@ -7970,7 +7961,7 @@
       <c r="G83" s="7"/>
     </row>
     <row r="84" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A84" s="115"/>
+      <c r="A84" s="112"/>
       <c r="B84" s="44" t="s">
         <v>145</v>
       </c>
@@ -7987,7 +7978,7 @@
       <c r="G84" s="13"/>
     </row>
     <row r="85" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A85" s="115"/>
+      <c r="A85" s="112"/>
       <c r="B85" s="44" t="s">
         <v>162</v>
       </c>
@@ -8002,7 +7993,7 @@
       <c r="G85" s="13"/>
     </row>
     <row r="86" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A86" s="115"/>
+      <c r="A86" s="112"/>
       <c r="B86" s="44" t="s">
         <v>188</v>
       </c>
@@ -8017,7 +8008,7 @@
       <c r="G86" s="13"/>
     </row>
     <row r="87" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A87" s="115"/>
+      <c r="A87" s="112"/>
       <c r="B87" s="44" t="s">
         <v>203</v>
       </c>
@@ -8032,7 +8023,7 @@
       <c r="G87" s="13"/>
     </row>
     <row r="88" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A88" s="115"/>
+      <c r="A88" s="112"/>
       <c r="B88" s="34"/>
       <c r="C88" s="85" t="s">
         <v>85</v>
@@ -8045,7 +8036,7 @@
       <c r="G88" s="10"/>
     </row>
     <row r="89" spans="1:7" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A89" s="115"/>
+      <c r="A89" s="112"/>
       <c r="B89" s="34"/>
       <c r="C89" s="85" t="s">
         <v>63</v>
@@ -8058,7 +8049,7 @@
       <c r="G89" s="10"/>
     </row>
     <row r="90" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A90" s="115"/>
+      <c r="A90" s="112"/>
       <c r="B90" s="34"/>
       <c r="C90" s="85" t="s">
         <v>88</v>
@@ -8071,7 +8062,7 @@
       <c r="G90" s="10"/>
     </row>
     <row r="91" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A91" s="115"/>
+      <c r="A91" s="112"/>
       <c r="B91" s="34"/>
       <c r="C91" s="85"/>
       <c r="D91" s="39"/>
@@ -8080,7 +8071,7 @@
       <c r="G91" s="10"/>
     </row>
     <row r="92" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A92" s="115"/>
+      <c r="A92" s="112"/>
       <c r="B92" s="34"/>
       <c r="C92" s="85"/>
       <c r="D92" s="39"/>
@@ -8089,7 +8080,7 @@
       <c r="G92" s="10"/>
     </row>
     <row r="93" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A93" s="115"/>
+      <c r="A93" s="112"/>
       <c r="B93" s="34"/>
       <c r="C93" s="85"/>
       <c r="D93" s="39"/>
@@ -8098,7 +8089,7 @@
       <c r="G93" s="10"/>
     </row>
     <row r="94" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A94" s="115"/>
+      <c r="A94" s="112"/>
       <c r="B94" s="36"/>
       <c r="C94" s="87"/>
       <c r="D94" s="50"/>
@@ -8107,37 +8098,37 @@
       <c r="G94" s="8"/>
     </row>
     <row r="95" spans="1:7" ht="30.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="122"/>
-      <c r="B95" s="112" t="s">
+      <c r="A95" s="119"/>
+      <c r="B95" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="C95" s="123" t="s">
+      <c r="C95" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="D95" s="123"/>
-      <c r="E95" s="113"/>
-      <c r="F95" s="114"/>
-      <c r="G95" s="114"/>
+      <c r="D95" s="120"/>
+      <c r="E95" s="110"/>
+      <c r="F95" s="111"/>
+      <c r="G95" s="111"/>
     </row>
     <row r="96" spans="1:7" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A96" s="115"/>
+      <c r="A96" s="112"/>
       <c r="B96" s="44" t="s">
         <v>163</v>
       </c>
       <c r="C96" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="124" t="s">
+      <c r="D96" s="121" t="s">
         <v>175</v>
       </c>
-      <c r="E96" s="110" t="s">
+      <c r="E96" s="107" t="s">
         <v>176</v>
       </c>
-      <c r="F96" s="111"/>
-      <c r="G96" s="111"/>
+      <c r="F96" s="108"/>
+      <c r="G96" s="108"/>
     </row>
     <row r="97" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A97" s="115"/>
+      <c r="A97" s="112"/>
       <c r="B97" s="44" t="s">
         <v>164</v>
       </c>
@@ -8154,7 +8145,7 @@
       <c r="G97" s="99"/>
     </row>
     <row r="98" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A98" s="115"/>
+      <c r="A98" s="112"/>
       <c r="B98" s="44" t="s">
         <v>165</v>
       </c>
@@ -8171,7 +8162,7 @@
       <c r="G98" s="99"/>
     </row>
     <row r="99" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A99" s="115"/>
+      <c r="A99" s="112"/>
       <c r="B99" s="44" t="s">
         <v>177</v>
       </c>
@@ -8188,7 +8179,7 @@
       <c r="G99" s="10"/>
     </row>
     <row r="100" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A100" s="115"/>
+      <c r="A100" s="112"/>
       <c r="B100" s="34"/>
       <c r="C100" s="80" t="s">
         <v>11</v>
@@ -8203,20 +8194,20 @@
       <c r="G100" s="99"/>
     </row>
     <row r="101" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A101" s="115"/>
-      <c r="B101" s="104" t="s">
+      <c r="A101" s="112"/>
+      <c r="B101" s="101" t="s">
         <v>200</v>
       </c>
       <c r="C101" s="80" t="s">
         <v>201</v>
       </c>
-      <c r="D101" s="125"/>
+      <c r="D101" s="122"/>
       <c r="E101" s="74"/>
-      <c r="F101" s="105"/>
+      <c r="F101" s="102"/>
       <c r="G101" s="99"/>
     </row>
     <row r="102" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A102" s="115"/>
+      <c r="A102" s="112"/>
       <c r="B102" s="44" t="s">
         <v>206</v>
       </c>
@@ -8226,7 +8217,7 @@
       <c r="D102" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="E102" s="102" t="s">
+      <c r="E102" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F102" s="10">
@@ -8236,12 +8227,12 @@
         <f>F102-H102</f>
         <v>86294058926</v>
       </c>
-      <c r="H102" s="107">
+      <c r="H102" s="104">
         <v>149491284984</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A103" s="115"/>
+      <c r="A103" s="112"/>
       <c r="B103" s="44" t="s">
         <v>210</v>
       </c>
@@ -8251,7 +8242,7 @@
       <c r="D103" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="E103" s="102" t="s">
+      <c r="E103" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F103" s="10">
@@ -8261,12 +8252,12 @@
         <f>F103-H103</f>
         <v>14058506935</v>
       </c>
-      <c r="H103" s="107">
+      <c r="H103" s="104">
         <v>17775898745</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A104" s="115"/>
+      <c r="A104" s="112"/>
       <c r="B104" s="44" t="s">
         <v>216</v>
       </c>
@@ -8276,7 +8267,7 @@
       <c r="D104" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="E104" s="102" t="s">
+      <c r="E104" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F104" s="10">
@@ -8285,20 +8276,20 @@
       <c r="G104" s="10">
         <v>0</v>
       </c>
-      <c r="H104" s="107"/>
+      <c r="H104" s="104"/>
     </row>
     <row r="105" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A105" s="115"/>
+      <c r="A105" s="112"/>
       <c r="B105" s="44" t="s">
         <v>221</v>
       </c>
       <c r="C105" s="80" t="s">
         <v>222</v>
       </c>
-      <c r="D105" s="125" t="s">
+      <c r="D105" s="122" t="s">
         <v>225</v>
       </c>
-      <c r="E105" s="102" t="s">
+      <c r="E105" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F105" s="10">
@@ -8308,12 +8299,12 @@
         <f>F105-H105</f>
         <v>42533404491.719978</v>
       </c>
-      <c r="H105" s="107">
+      <c r="H105" s="104">
         <v>35458739621.560005</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A106" s="115"/>
+      <c r="A106" s="112"/>
       <c r="B106" s="44" t="s">
         <v>231</v>
       </c>
@@ -8326,7 +8317,7 @@
       <c r="E106" s="74" t="s">
         <v>176</v>
       </c>
-      <c r="F106" s="105">
+      <c r="F106" s="102">
         <f>(22680000000-9278539200)*1.6</f>
         <v>21442337280</v>
       </c>
@@ -8334,12 +8325,12 @@
         <f>F106-H106</f>
         <v>21442337280</v>
       </c>
-      <c r="H106" s="107">
+      <c r="H106" s="104">
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A107" s="115"/>
+      <c r="A107" s="112"/>
       <c r="B107" s="34"/>
       <c r="C107" s="85" t="s">
         <v>12</v>
@@ -8352,7 +8343,7 @@
       <c r="G107" s="10"/>
     </row>
     <row r="108" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A108" s="115"/>
+      <c r="A108" s="112"/>
       <c r="B108" s="34"/>
       <c r="C108" s="85" t="s">
         <v>13</v>
@@ -8365,7 +8356,7 @@
       <c r="G108" s="10"/>
     </row>
     <row r="109" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A109" s="115"/>
+      <c r="A109" s="112"/>
       <c r="B109" s="34"/>
       <c r="C109" s="85" t="s">
         <v>14</v>
@@ -8378,7 +8369,7 @@
       <c r="G109" s="10"/>
     </row>
     <row r="110" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A110" s="115"/>
+      <c r="A110" s="112"/>
       <c r="B110" s="34"/>
       <c r="C110" s="85" t="s">
         <v>38</v>
@@ -8391,7 +8382,7 @@
       <c r="G110" s="10"/>
     </row>
     <row r="111" spans="1:8" ht="45" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A111" s="115"/>
+      <c r="A111" s="112"/>
       <c r="B111" s="34"/>
       <c r="C111" s="85" t="s">
         <v>21</v>
@@ -8404,7 +8395,7 @@
       <c r="G111" s="10"/>
     </row>
     <row r="112" spans="1:8" ht="30" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A112" s="115"/>
+      <c r="A112" s="112"/>
       <c r="B112" s="34"/>
       <c r="C112" s="86" t="s">
         <v>22</v>
@@ -8417,10 +8408,10 @@
       <c r="G112" s="16"/>
     </row>
     <row r="113" spans="1:7" ht="30.75" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="122"/>
+      <c r="A113" s="119"/>
       <c r="B113" s="37"/>
-      <c r="C113" s="126"/>
-      <c r="D113" s="127"/>
+      <c r="C113" s="123"/>
+      <c r="D113" s="124"/>
       <c r="E113" s="73"/>
       <c r="F113" s="12"/>
       <c r="G113" s="12"/>
@@ -8521,22 +8512,22 @@
     <row r="1" spans="1:6" ht="28.5" x14ac:dyDescent="0.75">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="268" t="s">
+      <c r="C1" s="270" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="268"/>
-      <c r="E1" s="268"/>
-      <c r="F1" s="269"/>
+      <c r="D1" s="270"/>
+      <c r="E1" s="270"/>
+      <c r="F1" s="271"/>
     </row>
     <row r="2" spans="1:6" ht="32.25" outlineLevel="1" x14ac:dyDescent="0.85">
       <c r="A2" s="5"/>
-      <c r="B2" s="270" t="s">
+      <c r="B2" s="272" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="270"/>
-      <c r="D2" s="270"/>
-      <c r="E2" s="270"/>
-      <c r="F2" s="271"/>
+      <c r="C2" s="272"/>
+      <c r="D2" s="272"/>
+      <c r="E2" s="272"/>
+      <c r="F2" s="273"/>
     </row>
     <row r="3" spans="1:6" ht="28.5" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5"/>
